--- a/ptolemy_geographica/topostext/unmapped_review.xlsx
+++ b/ptolemy_geographica/topostext/unmapped_review.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:K86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -425,6 +425,9 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,21 +471,36 @@
           <t>lat_ptolemy</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>topostext_match_score</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topostext_name</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>topostext_ref</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2.03.21.02</t>
+          <t>2.11.03.04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Salinae</t>
+          <t>Erste Landspitze nach der Landspitze</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>coast</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,30 +510,43 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>EU01</t>
+          <t>EU04</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>39.3333333333333</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>55.6666666666667</t>
+          <t>58.25</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Its easternmost point</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2.11.2.5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2.05.04.05</t>
+          <t>2.15.06.01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tagus (Grenzpunkt Lusitania, Tarraconensis)</t>
+          <t>Berbis (Bebbis)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -530,77 +561,99 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>EU02</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tejo</t>
-        </is>
-      </c>
+          <t>EU05</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>40.1666666666667</t>
+          <t>46.0</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>above-mentioned western limit point through Mt. Albanus as far as the Bebia mountains and the border of Lower Pannoniaat</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2.14.1.1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2.06.70.02</t>
+          <t>4.07.07.02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aquae Calidae</t>
+          <t>Sabastrikon-Mündung</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>river_mouth</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>EU02</t>
+          <t>AF04</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>16.6666666666667</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>42.1666666666667</t>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sabastikon mouth</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>4.7.7.2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2.06.70.04</t>
+          <t>2.07.04.04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Baecula (Becula)</t>
+          <t>Pyrene-Gebirge (Grenzpunkt Aquitania, Narbonensis)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -610,30 +663,47 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EU02</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>EU03</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pyrenäen</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>43.1666666666667</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>then part of Narbonensis until the point of the Pyrenees</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2.7.3.2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2.06.70.05</t>
+          <t>2.08.14.08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gerunda</t>
+          <t>Forum Segusiavorum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -648,34 +718,47 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EU02</t>
+          <t>EU03</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Feurs</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>16.6666666666667</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>42.6666666666667</t>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Forum Segusianorum</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2.8.11.3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2.06.76.03</t>
+          <t>2.11.34.04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Inseln der Götter (2)</t>
+          <t>Scandia N</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -690,72 +773,94 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EU02</t>
+          <t>EU04</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.66666666666667</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>43.3333333333333</t>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>the northernmost point</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2.11.16.6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2.07.04.04</t>
+          <t>4.01.02.05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pyrene-Gebirge (Grenzpunkt Aquitania, Narbonensis)</t>
+          <t>Handelsbucht</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mountain</t>
+          <t>coast</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EU03</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Pyrenäen</t>
-        </is>
-      </c>
+          <t>AF01</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>6.16666666666667</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>43.1666666666667</t>
+          <t>34.3333333333333</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Emporikos kolpos</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>4.1.2.5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2.07.11.02</t>
+          <t>4.02.30.01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Divona</t>
+          <t>Thudaka (Thukada)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -765,123 +870,150 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>EU03</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Cahors</t>
-        </is>
-      </c>
+          <t>AF01</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>20.8333333333333</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>31.3333333333333</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Thibinia</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>4.2.28.6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2.08.03.02</t>
+          <t>4.03.43.02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sequana (Mitte)</t>
+          <t>Sikapha (Sykapha)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>river</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>EU03</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Seine</t>
-        </is>
-      </c>
+          <t>AF02</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>43.1666666666667</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>49.3333333333333</t>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sycapha</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>4.3.43.2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2.08.04.03</t>
+          <t>5.06.09.06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cebenna-Gebirge (Mitte)</t>
+          <t>Sebastopolis 2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mountain</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>EU03</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Cevennen</t>
-        </is>
-      </c>
+          <t>AS01</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>42.3333333333333</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Choloe or Chologi</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>5.6.9.5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2.08.14.08</t>
+          <t>2.06.70.05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Forum Segusiavorum</t>
+          <t>Gerunda</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -896,34 +1028,47 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>EU03</t>
+          <t>EU02</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Feurs</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>16.6666666666667</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>42.6666666666667</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Celsa</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2.6.67.2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2.09.10.03</t>
+          <t>2.09.18.03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Castellum</t>
+          <t>Elcebus</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -941,31 +1086,40 @@
           <t>EU03</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Cassel</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>52.25</t>
+          <t>47.0</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>42</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Helcebus</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2.9.9.6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2.09.16.02</t>
+          <t>4.03.30.12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Traiana, Legio XXII Primigenia</t>
+          <t>Thamugadi</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -975,35 +1129,52 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>EU03</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>AF02</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Timgad</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>50.5833333333333</t>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Ammaedara</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>4.3.30.9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2.09.18.03</t>
+          <t>5.04.06.07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Elcebus</t>
+          <t>Eusene</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1013,35 +1184,48 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>EU03</t>
+          <t>AS01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>64.6666666666667</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>42.6666666666667</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Titoua</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>5.4.6.6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2.10.13.02</t>
+          <t>2.15.06.04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Noviomagus</t>
+          <t>Cirtisa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1056,35 +1240,52 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>EU03</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+          <t>EU05</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>bei Dakovo</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>42.3333333333333</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.3333333333333</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Adra</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2.16.10.1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2.11.03.01</t>
+          <t>3.13.42.03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nächste und nördlichste Landspitze</t>
+          <t>Azoros</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>coast</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1094,35 +1295,52 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EU04</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+          <t>EU10</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vuvala</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>38.6666666666667</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>58.1666666666667</t>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>In Tymphaia: Gyrtone</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>3.12.40.1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2.11.03.04</t>
+          <t>2.06.70.02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Erste Landspitze nach der Landspitze</t>
+          <t>Aquae Calidae</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>coast</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1132,30 +1350,43 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>EU04</t>
+          <t>EU02</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>39.3333333333333</t>
+          <t>16.6666666666667</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>58.25</t>
+          <t>42.1666666666667</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Burtina</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2.6.67.7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2.11.29.11</t>
+          <t>3.08.09.06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bergium</t>
+          <t>Hydata</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1170,35 +1401,48 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EU04</t>
+          <t>EU09</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>45.6666666666667</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Germizera</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>3.8.4.21</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2.11.34.04</t>
+          <t>2.09.16.02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Scandia N</t>
+          <t>Traiana, Legio XXII Primigenia</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>island</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1208,77 +1452,99 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>EU04</t>
+          <t>EU03</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>27.5</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>50.5833333333333</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>In the zone below this, the cities are as follows: Aleison</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2.11.14.1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2.15.02.05</t>
+          <t>4.03.37.02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Danuvius (Einmündung des Dravus)</t>
+          <t>Almaina (Almina)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>river</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EU05</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Donau (Einmündung der Drau)</t>
-        </is>
-      </c>
+          <t>AF02</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>44.3333333333333</t>
+          <t>35.25</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>45.6666666666667</t>
+          <t>30.67777777</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Below Adrumetum city: Almaena</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>4.3.37.1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2.15.02.12</t>
+          <t>2.11.03.01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Danuvius (Biegung bei Cornacum)</t>
+          <t>Nächste und nördlichste Landspitze</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>river</t>
+          <t>coast</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1288,35 +1554,48 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>EU05</t>
+          <t>EU04</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>44.4166666666667</t>
+          <t>38.6666666666667</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>58.1666666666667</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>The next and northernmost promontory</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2.11.2.3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2.15.02.14</t>
+          <t>2.10.13.02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Danuvius (Biegung bei Acumincum)</t>
+          <t>Noviomagus</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>river</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1326,39 +1605,48 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>EU05</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Donau</t>
-        </is>
-      </c>
+          <t>EU03</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
+          <t>23.5</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>45.0</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>45.4166666666667</t>
+      <c r="I23" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>to these and towards Belgica are the Vadicasii and their city Noeomagus</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2.8.11.5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2.15.02.16</t>
+          <t>3.10.08.04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Danuvius (Biegung bei Rittium)</t>
+          <t>Histria</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>river</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1368,34 +1656,47 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>EU05</t>
+          <t>EU09</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Donau</t>
+          <t>Carnasuf</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>55.6666666666667</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.0</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Tibiska</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>3.10.6.2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2.15.04.03</t>
+          <t>2.05.04.05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Solva</t>
+          <t>Tagus (Grenzpunkt Lusitania, Tarraconensis)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1410,118 +1711,141 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>EU05</t>
+          <t>EU02</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Esztergom</t>
+          <t>Tejo</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>40.1666666666667</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Obila</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2.5.7.10</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2.15.04.05</t>
+          <t>4.02.16.02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aquincum</t>
+          <t>Phruraison-Gebirge (O-Ende)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>EU05</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Budapest</t>
-        </is>
-      </c>
+          <t>AF01</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>4.2.16.2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2.15.04.06</t>
+          <t>4.07.26.03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vetus Salina</t>
+          <t>Äthiopische Berge (S-Ende)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>EU05</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Adony</t>
-        </is>
-      </c>
+          <t>AF04</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>4.7.26.2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2.15.04.07</t>
+          <t>4.05.25.02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lussonium</t>
+          <t>Oasiten (Thasioten)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1531,81 +1855,103 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>EU05</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Dunakömlöd</t>
-        </is>
-      </c>
+          <t>AF03</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>27.8333333333333</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Big Oasis</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>4.5.37.2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2.15.05.01</t>
+          <t>4.03.44.05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lugio</t>
+          <t>Aigimoros</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>island</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>EU05</t>
+          <t>AF02</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dunaszekcsö</t>
+          <t>Ile Zembra</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>33.25</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Kalathe</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>4.3.44.2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2.15.05.02</t>
+          <t>3.08.08.07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Teutoburgium</t>
+          <t>Pirum</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1620,34 +1966,43 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>EU05</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Dalj</t>
-        </is>
-      </c>
+          <t>EU09</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>51.25</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>45.6666666666667</t>
+          <t>46.0</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Komidaua</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>3.8.4.22</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2.15.05.03</t>
+          <t>2.09.10.03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cornacum</t>
+          <t>Castellum</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1662,156 +2017,212 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>EU05</t>
+          <t>EU03</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sotin</t>
+          <t>Cassel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>44.3333333333333</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>52.25</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Tabula River the Tungriand their city Atuatucum</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2.9.5.1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2.15.05.04</t>
+          <t>4.04.08.01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Acumincum</t>
+          <t>Dünen des Herakles (Mitte)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>river</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>EU05</t>
+          <t>AF03</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stari Slankamen</t>
+          <t>Ras Carcura</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>44.8333333333333</t>
+          <t>48.6666666666667</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>45.3333333333333</t>
+          <t>29.0</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>The province has mountains, the so-called Dunes of Herakles, midpoint</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>4.4.8.1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2.15.05.05</t>
+          <t>4.03.46.02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Rittium</t>
+          <t>Pontia</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>island</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>EU05</t>
+          <t>AF02</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Surduk</t>
+          <t>Tre Scogli</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.3333333333333</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>30.25</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Altars of Philainostoward the south to the end point at</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>4.4.1.1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2.15.06.01</t>
+          <t>5.06.01.13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Berbis (Bebbis)</t>
+          <t>Euphrat (Biegung nach Osten)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>river</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>EU05</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
+          <t>AS01</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Euphrat</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>north, it is then deflected from the east, the location of which is</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>5.6.1.4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2.15.06.02</t>
+          <t>2.06.70.04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Servitium*</t>
+          <t>Baecula (Becula)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1826,39 +2237,48 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>EU05</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Bosanska Gradiska</t>
-        </is>
-      </c>
+          <t>EU02</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>42.3333333333333</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>42.25</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Egosa</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2.6.70.3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2.15.06.03</t>
+          <t>2.08.04.03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Iovalia</t>
+          <t>Cebenna-Gebirge (Mitte)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1868,34 +2288,47 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>EU05</t>
+          <t>EU03</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Valpovo</t>
+          <t>Cevennen</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>42.3333333333333</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.5</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>East of the Arverni until the northward turn of the river Rhone, is the tribe of the Aedui and their cities: Augustodunum</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2.8.12.1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2.15.06.04</t>
+          <t>2.15.04.03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cirtisa</t>
+          <t>Solva</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1915,29 +2348,42 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>bei Dakovo</t>
+          <t>Esztergom</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>42.3333333333333</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>45.3333333333333</t>
+          <t>47.5</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>The next turn at Carpis, which is the most northerly of all</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2.11.3.9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2.15.07.01</t>
+          <t>2.15.08.02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mursella</t>
+          <t>Sallis (Saldis)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1955,31 +2401,40 @@
           <t>EU05</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Petrijevci</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>44.6666666666667</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Sidrona</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2.16.10.5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2.15.07.02</t>
+          <t>2.15.08.05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cibalae</t>
+          <t>Sirmium*</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1999,34 +2454,47 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vinkovci</t>
+          <t>Sremska Mitrovica</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>44.8333333333333</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.0</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>that point where the Arabus river flows into the Danube, forming those borders to which we have referred; on the south by Illyria which extends from the indicated terminus as far as the bend in the Danube near which the Savos river empties into it</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2.15.1.1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2.15.07.04</t>
+          <t>3.01.80.02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vacontium (Vocantium)</t>
+          <t>Diomedische Inseln (5)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>island</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2036,30 +2504,47 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>EU05</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
+          <t>EU06</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Isole di Tremiti</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>40.6666666666667</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>43.0</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>of the Maurrucini on the same gulf mouth of the Aternus river</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>3.1.20.1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2.15.08.01</t>
+          <t>4.05.76.03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mursa (Mursa*)</t>
+          <t>Argaiu</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2069,44 +2554,53 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>EU05</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Osijek</t>
-        </is>
-      </c>
+          <t>AF03</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>61.4166666666667</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>31.6666666666667</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>the Sebennytic mouth</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>4.5.10.3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2.15.08.02</t>
+          <t>2.08.03.02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sallis (Saldis)</t>
+          <t>Sequana (Mitte)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>river</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2116,30 +2610,47 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>EU05</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
+          <t>EU03</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Seine</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>44.6666666666667</t>
+          <t>49.3333333333333</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Below these are the Vessones, with their city similarly on the eastern side of the SequanaRiver, Augusta Vessonum</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2.9.6.4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2.15.08.05</t>
+          <t>2.07.11.02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sirmium*</t>
+          <t>Divona</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2154,39 +2665,52 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>EU05</t>
+          <t>EU03</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sremska Mitrovica</t>
+          <t>Cahors</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>44.8333333333333</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>47.25</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>to these the Cadurci and their city Dueona</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2.7.6.6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3.01.80.02</t>
+          <t>2.15.06.02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Diomedische Inseln (5)</t>
+          <t>Servitium*</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>island</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2196,123 +2720,158 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>EU06</t>
+          <t>EU05</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Isole di Tremiti</t>
+          <t>Bosanska Gradiska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>40.6666666666667</t>
+          <t>42.3333333333333</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>46.5</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>30</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>On the north, by the above-mentioned border of Noricum and by the part of the Danubebetween Cetium mountain and the junction with the Arabon river</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2.14.1.2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3.05.02.01</t>
+          <t>4.07.25.03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vistula-Mündung</t>
+          <t>Maste</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>river_mouth</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>EU08</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Weichsel-Mündung</t>
-        </is>
-      </c>
+          <t>AF04</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>-4.25</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>30</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>the more eastern lake</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>4.7.24.2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3.05.06.02</t>
+          <t>4.03.28.05</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sarmatische Berge (S-Ende)</t>
+          <t>Mileum</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>mountain</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>EU08</t>
+          <t>AF02</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Westkarpaten</t>
+          <t>Mila</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>26.6666666666667</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>30.3333333333333</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Lares</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>4.3.28.4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3.05.15.04</t>
+          <t>2.15.04.06</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Amadoka-Gebirge</t>
+          <t>Vetus Salina</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>mountain</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2322,30 +2881,47 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>EU08</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
+          <t>EU05</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Adony</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>47.0</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Sidrona</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2.16.10.5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3.08.08.07</t>
+          <t>2.15.06.03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pirum</t>
+          <t>Iovalia</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2360,35 +2936,52 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>EU09</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
+          <t>EU05</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Valpovo</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>51.25</t>
+          <t>42.3333333333333</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>46.0</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Salvia</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2.16.9.8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3.08.09.06</t>
+          <t>2.15.02.05</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hydata</t>
+          <t>Danuvius (Einmündung des Dravus)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>river</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2398,35 +2991,52 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>EU09</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
+          <t>EU05</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Donau (Einmündung der Drau)</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>44.3333333333333</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>45.6666666666667</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>27</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Adra</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2.16.10.1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3.10.08.04</t>
+          <t>2.15.02.14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Histria</t>
+          <t>Danuvius (Biegung bei Acumincum)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>river</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2436,34 +3046,47 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>EU09</t>
+          <t>EU05</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Carnasuf</t>
+          <t>Donau</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>55.6666666666667</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.4166666666667</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>27</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>that point where the Arabus river flows into the Danube, forming those borders to which we have referred; on the south by Illyria which extends from the indicated terminus as far as the bend in the Danube near which the Savos river empties into it</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2.15.1.1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3.13.42.03</t>
+          <t>2.15.08.01</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Azoros</t>
+          <t>Mursa (Mursa*)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2478,72 +3101,98 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>EU10</t>
+          <t>EU05</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vuvala</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>45.75</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>27</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>The bend at Curta</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2.11.3.8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4.01.02.05</t>
+          <t>2.03.21.02</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Handelsbucht</t>
+          <t>Salinae</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>coast</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AF01</t>
+          <t>EU01</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>6.16666666666667</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>34.3333333333333</t>
+          <t>55.6666666666667</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Navalia</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2.11.13.2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4.02.12.03</t>
+          <t>2.15.04.05</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Grenzpunkt (Africa, Inneres Libyen, Mauretania Caesariensis)</t>
+          <t>Aquincum</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2553,78 +3202,108 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AF01</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
+          <t>EU05</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>27.8333333333333</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>47.5</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Anavum</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2.11.15.19</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4.02.16.02</t>
+          <t>2.11.29.11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Phruraison-Gebirge (O-Ende)</t>
+          <t>Bergium</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>mountain</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AF01</t>
+          <t>EU04</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>49.5</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>further the mountains called the Sudeta, whose extremities occupy the positions</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2.11.5.9</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4.02.30.01</t>
+          <t>4.03.18.05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Thudaka (Thukada)</t>
+          <t>Uasalaiton-Gebirge (W-Ende)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2634,30 +3313,43 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AF01</t>
+          <t>AF02</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20.8333333333333</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>31.3333333333333</t>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Tisurus</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>4.3.38.5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4.03.01.05</t>
+          <t>2.15.05.03</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Grenzpunkt (Africa, Inneres Libyen, Mauretania Caesariensis)</t>
+          <t>Cornacum</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2667,116 +3359,167 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AF02</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
+          <t>EU05</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Sotin</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>27.8333333333333</t>
+          <t>44.3333333333333</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>45.25</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Nedinon</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2.16.10.8</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4.03.18.05</t>
+          <t>2.15.02.16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Uasalaiton-Gebirge (W-Ende)</t>
+          <t>Danuvius (Biegung bei Rittium)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>mountain</t>
+          <t>river</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AF02</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
+          <t>EU05</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Donau</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>45.0</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>24</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>that point where the Arabus river flows into the Danube, forming those borders to which we have referred; on the south by Illyria which extends from the indicated terminus as far as the bend in the Danube near which the Savos river empties into it</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2.15.1.1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4.03.20.03</t>
+          <t>2.15.07.02</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Thizibi-Berg</t>
+          <t>Cibalae</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>mountain</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AF02</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
+          <t>EU05</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vinkovci</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Adra</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2.16.10.1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4.03.28.05</t>
+          <t>4.03.20.03</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mileum</t>
+          <t>Thizibi-Berg</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2789,116 +3532,151 @@
           <t>AF02</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Mila</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>26.6666666666667</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>30.3333333333333</t>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Mt. Thizibi</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>4.3.20.2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4.03.30.12</t>
+          <t>2.06.76.03</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Thamugadi</t>
+          <t>Inseln der Götter (2)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>island</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AF02</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Timgad</t>
-        </is>
-      </c>
+          <t>EU02</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>4.66666666666667</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>43.3333333333333</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Limios river mouth</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2.6.1.4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4.03.37.02</t>
+          <t>3.05.06.02</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Almaina (Almina)</t>
+          <t>Sarmatische Berge (S-Ende)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AF02</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
+          <t>EU08</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Westkarpaten</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>30.67777777</t>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>There are the following cities among the Migratory Iazuges: Ouskenon</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>3.7.2.1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4.03.43.02</t>
+          <t>4.06.09.03</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sikapha (Sykapha)</t>
+          <t>Kapha-Gebirge (Mitte)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2908,161 +3686,213 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AF02</t>
+          <t>AF04</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>43.1666666666667</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>which the Stacheir river flows, forming lake Klonia beside it, midpoint</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>4.6.8.3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4.03.44.05</t>
+          <t>2.15.07.01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Aigimoros</t>
+          <t>Mursella</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>island</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AF02</t>
+          <t>EU05</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ile Zembra</t>
+          <t>Petrijevci</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>46.0</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Salvia</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2.16.9.8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4.03.46.02</t>
+          <t>2.15.05.04</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Pontia</t>
+          <t>Acumincum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>island</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AF02</t>
+          <t>EU05</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tre Scogli</t>
+          <t>Stari Slankamen</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
+          <t>44.8333333333333</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
           <t>45.3333333333333</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>30.25</t>
+      <c r="I64" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>that point where the Arabus river flows into the Danube, forming those borders to which we have referred; on the south by Illyria which extends from the indicated terminus as far as the bend in the Danube near which the Savos river empties into it</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2.15.1.1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4.04.08.01</t>
+          <t>2.15.05.05</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Dünen des Herakles (Mitte)</t>
+          <t>Rittium</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>river</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AF03</t>
+          <t>EU05</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ras Carcura</t>
+          <t>Surduk</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>48.6666666666667</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>45.0</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>that point where the Arabus river flows into the Danube, forming those borders to which we have referred; on the south by Illyria which extends from the indicated terminus as far as the bend in the Danube near which the Savos river empties into it</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2.15.1.1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4.05.25.02</t>
+          <t>4.07.11.08</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Oasiten (Thasioten)</t>
+          <t>Kleiner Strand</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>coast</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3072,30 +3902,43 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AF03</t>
+          <t>AF04</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>27.8333333333333</t>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>South horn promontory</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>4.7.11.6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4.05.76.03</t>
+          <t>2.15.04.07</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Argaiu</t>
+          <t>Lussonium</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3105,40 +3948,57 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AF03</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
+          <t>EU05</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Dunakömlöd</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>61.4166666666667</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>31.6666666666667</t>
+          <t>46.75</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Sidrona</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2.16.10.5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4.06.08.05</t>
+          <t>4.02.12.03</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sagapola-Gebirge (Mitte)</t>
+          <t>Grenzpunkt (Africa, Inneres Libyen, Mauretania Caesariensis)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>mountain</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3148,35 +4008,48 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AF04</t>
+          <t>AF01</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>27.8333333333333</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>It is bounded on the east by Africa along the Ampsagas river to that point at</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>4.2.12.1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4.06.09.03</t>
+          <t>4.03.01.05</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Kapha-Gebirge (Mitte)</t>
+          <t>Grenzpunkt (Africa, Inneres Libyen, Mauretania Caesariensis)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>mountain</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3186,68 +4059,94 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AF04</t>
+          <t>AF02</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>27.8333333333333</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>It is bounded on the east by Africa along the Ampsagas river to that point at</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>4.2.12.1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4.06.27.05</t>
+          <t>2.15.02.12</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Uellegeia (Uelegeia)</t>
+          <t>Danuvius (Biegung bei Cornacum)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>river</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AF04</t>
+          <t>EU05</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>44.4166666666667</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>11.6666666666667</t>
+          <t>45.25</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Nedinon</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2.16.10.8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4.06.28.01</t>
+          <t>2.15.05.01</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Thupai (Thuppai)</t>
+          <t>Lugio</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3257,192 +4156,259 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AF04</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
+          <t>EU05</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Dunaszekcsö</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>16.6666666666667</t>
+          <t>46.5</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>15</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Sidrona</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2.16.10.5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>4.07.07.02</t>
+          <t>2.15.05.02</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sabastrikon-Mündung</t>
+          <t>Teutoburgium</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>river_mouth</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AF04</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
+          <t>EU05</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Dalj</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>45.6666666666667</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Bournon</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2.16.10.4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4.07.11.06</t>
+          <t>3.05.15.04</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Apokopon (Apokopa)</t>
+          <t>Amadoka-Gebirge</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>coast</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AF04</t>
+          <t>EU08</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Bykos river mouth</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>3.5.4.4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4.07.11.08</t>
+          <t>2.15.07.04</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Kleiner Strand</t>
+          <t>Vacontium (Vocantium)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>coast</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AF04</t>
+          <t>EU05</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>46.5</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>The bend at Curta</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2.11.3.8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4.07.11.09</t>
+          <t>3.05.02.01</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Grosser Strand</t>
+          <t>Vistula-Mündung</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>coast</t>
+          <t>river_mouth</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AF04</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
+          <t>EU08</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Weichsel-Mündung</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2.0</t>
-        </is>
-      </c>
+          <t>56.0</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4.07.11.10</t>
+          <t>4.06.08.05</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Essina (Essinadu)</t>
+          <t>Sagapola-Gebirge (Mitte)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>coast</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3455,36 +4421,45 @@
           <t>AF04</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Wasin</t>
-        </is>
-      </c>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>73.1666666666667</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Thuelath or Thuoilath</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>4.6.24.2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4.07.24.03</t>
+          <t>4.06.27.05</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Koloe-See</t>
+          <t>Uellegeia (Uelegeia)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>lake</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3500,24 +4475,27 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>11.6666666666667</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4.07.25.02</t>
+          <t>4.06.28.01</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Koloe</t>
+          <t>Thupai (Thuppai)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3538,29 +4516,42 @@
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>16.6666666666667</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Nigeira metropolis</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>4.6.27.4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4.07.25.03</t>
+          <t>4.07.11.06</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Maste</t>
+          <t>Apokopon (Apokopa)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>coast</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3576,29 +4567,42 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Zingis promontory</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>4.7.11.3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4.07.26.03</t>
+          <t>4.07.11.09</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Äthiopische Berge (S-Ende)</t>
+          <t>Grosser Strand</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>mountain</t>
+          <t>coast</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3614,29 +4618,32 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>8.0</t>
-        </is>
-      </c>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4.07.26.07</t>
+          <t>4.07.11.10</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Pylaia-Gebirge</t>
+          <t>Essina (Essinadu)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>mountain</t>
+          <t>coast</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3649,32 +4656,39 @@
           <t>AF04</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Wasin</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>73.1666666666667</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4.07.26.08</t>
+          <t>4.07.24.03</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Maste-Berg</t>
+          <t>Koloe-See</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>mountain</t>
+          <t>lake</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3690,29 +4704,32 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-5.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4.08.06.01</t>
+          <t>4.07.25.02</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Dauchis-Gebirge (Mitte)</t>
+          <t>Koloe</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>mountain</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3728,132 +4745,150 @@
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-13.0</t>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Maste city</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>4.7.25.3</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5.04.06.07</t>
+          <t>4.07.26.07</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Eusene</t>
+          <t>Pylaia-Gebirge</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AS01</t>
+          <t>AF04</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>64.6666666666667</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>42.6666666666667</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5.06.01.13</t>
+          <t>4.07.26.08</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Euphrat (Biegung nach Osten)</t>
+          <t>Maste-Berg</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>river</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AS01</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Euphrat</t>
-        </is>
-      </c>
+          <t>AF04</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>42.5</t>
-        </is>
-      </c>
+          <t>-5.0</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5.06.09.06</t>
+          <t>4.08.06.01</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sebastopolis 2</t>
+          <t>Dauchis-Gebirge (Mitte)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AS01</t>
+          <t>AF04</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>42.3333333333333</t>
-        </is>
-      </c>
+          <t>-13.0</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3866,7 +4901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3878,6 +4913,9 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3926,6 +4964,21 @@
           <t>lat_decimal</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>catalogue_match_score</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>catalogue_name</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>catalogue_ref_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3935,42 +4988,55 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>are the Catuvellauni, among whom are the towns: Salinae</t>
+          <t>Legion I Athena (Minerva) and then Traiane Legion</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20°45'</t>
+          <t>28°30'</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>55°50'</t>
+          <t>50°35'</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>55.8333</t>
+          <t>50.5833</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Bonna, Legio I Minervia</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2.09.16.01</t>
         </is>
       </c>
     </row>
@@ -3987,37 +5053,50 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saitabis</t>
+          <t>Edeta and/or Leiria</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13°10'</t>
+          <t>14°20'</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>37°00'</t>
+          <t>38°25'</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>13.1667</t>
+          <t>14.3333</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>38.4167</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Edeta bzw. Liria</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2.06.63.14</t>
         </is>
       </c>
     </row>
@@ -4029,42 +5108,55 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Edeta and/or Leiria</t>
+          <t>Forum Segusianorum</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14°20'</t>
+          <t>20°30'</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>38°25'</t>
+          <t>45°30'</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>14.3333</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>38.4167</t>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Forum Segusiavorum</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2.08.14.08</t>
         </is>
       </c>
     </row>
@@ -4076,12 +5168,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4091,27 +5183,40 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>The eastern side adjoins the part of Lugdunensis by the Liger River until its head</t>
+          <t>mouths of the river Rhenus: Mouths of the river Vidrus</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20°00'</t>
+          <t>27°20'</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>44°30'</t>
+          <t>54°45'</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>27.3333</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>54.75</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>43</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Vidrus-Mündung</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2.11.01.05</t>
         </is>
       </c>
     </row>
@@ -4123,49 +5228,62 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>to these the Cadurci and their city Dueona</t>
+          <t>the northernmost point</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19°00'</t>
+          <t>44°20'</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>46°15'</t>
+          <t>58°20'</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>44.3333</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>58.3333</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Scandia N</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2.11.34.04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4180,143 +5298,182 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The southern side is bounded by the part on this side of Narbonensis as far as the mentioned end point by Aquitania, the Cemmena mountains, mid-point</t>
+          <t>Argidaua</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20°20'</t>
+          <t>46°30'</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>44°30'</t>
+          <t>45°15'</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20.3333</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>45.25</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Lizisis (Aizisis)</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>3.08.09.02</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forum Segusianorum</t>
+          <t>Emporikos kolpos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20°30'</t>
+          <t>6°30'</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>45°30'</t>
+          <t>34°20'</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>34.3333</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Handelsbucht</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>4.01.02.05</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mosa River the Menapii and their city Castellum</t>
+          <t>Kadmos mountain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>25°00'</t>
+          <t>59°40'</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>22°15'</t>
+          <t>37°40'</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>59.6667</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>37.6667</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Grenzpunkt (eigentliches Asien, Lykien 2)</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>5.02.12.04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4326,27 +5483,40 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Legion I Athena (Minerva) and then Traiane Legion</t>
+          <t>along the line of the Moschikos mountains and to the terminal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>28°30'</t>
+          <t>73°00'</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>50°35'</t>
+          <t>44°30'</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50.5833</t>
+          <t>44.5</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Xyline</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>5.06.06.08</t>
         </is>
       </c>
     </row>
@@ -4358,89 +5528,115 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>mouths of the river Rhenus: Mouths of the river Vidrus</t>
+          <t>to these the Cadurci and their city Dueona</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>27°20'</t>
+          <t>19°00'</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>54°45'</t>
+          <t>46°15'</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>27.3333</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>54.75</t>
+          <t>46.25</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Cossium</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2.07.15.02</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>turn</t>
+          <t>Laodikeia katakekaumene</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>39°10'</t>
+          <t>63°40'</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>59°10'</t>
+          <t>39°40'</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>39.1667</t>
+          <t>63.6667</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>59.1667</t>
+          <t>39.6667</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>verbranntes' Laodikeia</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>5.04.10.11</t>
         </is>
       </c>
     </row>
@@ -4452,42 +5648,55 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bergium</t>
+          <t>are the Catuvellauni, among whom are the towns: Salinae</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>33°00'</t>
+          <t>20°45'</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>49°20'</t>
+          <t>55°50'</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>49.3333</t>
+          <t>55.8333</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metaris-Ästuar</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2.03.06.07</t>
         </is>
       </c>
     </row>
@@ -4499,49 +5708,62 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>the northernmost point</t>
+          <t>The eastern side adjoins the part of Lugdunensis by the Liger River until its head</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>44°20'</t>
+          <t>20°00'</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>58°20'</t>
+          <t>44°30'</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>44.3333</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>58.3333</t>
+          <t>44.5</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Tolosa</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2.10.09.05</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4556,455 +5778,577 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Piroum</t>
+          <t>The southern side is bounded by the part on this side of Narbonensis as far as the mentioned end point by Aquitania, the Cemmena mountains, mid-point</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>51°15'</t>
+          <t>20°20'</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6°00'</t>
+          <t>44°30'</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>51.25</t>
+          <t>20.3333</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>44.5</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Tolosa</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2.10.09.05</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Argidaua</t>
+          <t>Saitabis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>46°30'</t>
+          <t>13°10'</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>45°15'</t>
+          <t>37°00'</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>13.1667</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Saetabis-Mündung</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2.06.14.07</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Hydata</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>49°30'</t>
+          <t>21°00'</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5°00'</t>
+          <t>26°00'</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Phruraison-Gebirge (O-Ende)</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>4.02.16.02</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>where the Moschios river branches. Viminacium, legion</t>
+          <t>a different starting point, the towns are Thudaca</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>46°30'</t>
+          <t>19°10'</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4°00'</t>
+          <t>32°20'</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>19.1667</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>32.3333</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Tigis</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>4.02.30.02</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>the more northerly of this division flows into Pontos by the mouth called Boreios, located</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>56°20'</t>
+          <t>55°00'</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6°50'</t>
+          <t>8°30'</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>56.3333</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>6.8333</t>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Äthiopische Berge (S-Ende)</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>4.07.26.03</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>the mor southerly of this division flows into Pontos by the mouth called Narakion</t>
+          <t>Altar of Eros promontory</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>56°10'</t>
+          <t>66°30'</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>6°20'</t>
+          <t>16°00'</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>56.1667</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6.3333</t>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Ptolemais Theron*</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>4.07.07.01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sacred mouth of the Istros river, Pteron promontory</t>
+          <t>Bergium</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>56°20'</t>
+          <t>33°00'</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>6°00'</t>
+          <t>49°20'</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>56.3333</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>49.3333</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Alpes (N-Spitzen)</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2.11.07.05</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Istros city</t>
+          <t>The Nitriotai, and the Oasita dwell in the parts still further to the south, at</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>55°40'</t>
+          <t>59°30'</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>6°00'</t>
+          <t>29°30'</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>55.6667</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Pharos</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>4.05.76.02</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Of the Pelagonians: Audaristos</t>
+          <t>Bunthum</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>48°40'</t>
+          <t>36°15'</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>50°05'</t>
+          <t>27°20'</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>48.6667</t>
+          <t>36.25</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>50.0833</t>
+          <t>27.3333</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Bunthon</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>4.03.36.07</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pherai</t>
+          <t>beside the lakes the so-called Pylaian mountains . 65°00' . equator and Maste mountain</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>49°30'</t>
+          <t>68°00'</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>30°15'</t>
+          <t>5°00'</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>26</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Garbato-Gebirge (Mitte)</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>4.07.26.04</t>
         </is>
       </c>
     </row>
@@ -5016,85 +6360,115 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Emporikos kolpos</t>
+          <t>Aigimoros island</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>6°30'</t>
+          <t>34°15'</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>34°20'</t>
+          <t>33°30'</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>34.3333</t>
+          <t>33.5</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Kap Hermaia</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>4.03.08.01</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Neapolis</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>21°00'</t>
+          <t>62°40'</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>26°00'</t>
+          <t>48°45'</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>62.6667</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>48.75</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>20</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Phanagoria</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>5.09.06.02</t>
         </is>
       </c>
     </row>
@@ -5106,136 +6480,175 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>a different starting point, the towns are Thudaca</t>
+          <t>Essina trading post</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>19°10'</t>
+          <t>73°30'</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>32°20'</t>
+          <t>3°30' S</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>19.1667</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>32.3333</t>
+          <t>-3.5</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Sarapion</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>4.07.11.11</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mt. Ousalaiton or Ousaleton, the end points of which are at</t>
+          <t>Of the Pelagonians: Audaristos</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>37°00'</t>
+          <t>48°40'</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>38°00'</t>
+          <t>50°05'</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>48.6667</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>50.0833</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>18</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Porolisson</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>3.08.06.04</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>which the Triton river flows, and in it these lakes: Tritonitis</t>
+          <t>turn</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>38°40'</t>
+          <t>39°10'</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>39°40'</t>
+          <t>59°10'</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>38.6667</t>
+          <t>39.1667</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>39.6667</t>
+          <t>59.1667</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Erste Landspitze nach der Landspitze</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2.11.03.04</t>
         </is>
       </c>
     </row>
@@ -5252,37 +6665,50 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bunthum</t>
+          <t>Pontia island</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>36°15'</t>
+          <t>45°20'</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>27°20'</t>
+          <t>20°15'</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>36.25</t>
+          <t>45.3333</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>27.3333</t>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Kinyps (O-Quelle)</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>4.06.11.03</t>
         </is>
       </c>
     </row>
@@ -5294,42 +6720,55 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aigimoros island</t>
+          <t>which the Subos river flows, midpoint</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>34°15'</t>
+          <t>20°20'</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>33°30'</t>
+          <t>22°</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>20.3333</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Byntha</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>4.06.25.05</t>
         </is>
       </c>
     </row>
@@ -5341,89 +6780,115 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pontia island</t>
+          <t>Small shore</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>45°20'</t>
+          <t>78°00'</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20°15'</t>
+          <t>1°00' S</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>45.3333</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>15</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Horn des Südens</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>4.07.11.07</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Anthedon</t>
+          <t>at the city Kytoron of the Pontos</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>64°50'</t>
+          <t>61°00'</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>51°40'</t>
+          <t>33°45'</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>64.8333</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>51.6667</t>
+          <t>33.75</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Xanthos-Mündung</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>5.03.02.07</t>
         </is>
       </c>
     </row>
@@ -5435,42 +6900,51 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>The Nitriotai, and the Oasita dwell in the parts still further to the south, at</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>59°30'</t>
+          <t>68°</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>29°30'</t>
+          <t>12°20' S</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>-12.3333</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Mondgebirge (O-Ende)</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>4.08.03.06</t>
         </is>
       </c>
     </row>
@@ -5487,37 +6961,50 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>same meridian until the limit, at</t>
+          <t>Uellegeia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>51°15'</t>
+          <t>28°30'</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3°10'</t>
+          <t>16°40'</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>51.25</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3.1667</t>
+          <t>16.6667</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>12</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Tagama</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>4.06.27.06</t>
         </is>
       </c>
     </row>
@@ -5529,59 +7016,72 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>which the Subos river flows, midpoint</t>
+          <t>Maste city</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>20°20'</t>
+          <t>65°00'</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>22°</t>
+          <t>4°15'</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>20.3333</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>8</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Koloe</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>4.07.25.02</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5591,405 +7091,432 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>which the Darados river flows, midpoint</t>
+          <t>Mosa River the Menapii and their city Castellum</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>27°</t>
+          <t>25°00'</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>10°</t>
+          <t>22°15'</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10.0</t>
-        </is>
-      </c>
+          <t>22.25</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Uellegeia</t>
+          <t>Piroum</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>28°30'</t>
+          <t>51°15'</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>16°40'</t>
+          <t>6°00'</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>51.25</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>16.6667</t>
-        </is>
-      </c>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>south of the river Thupai</t>
+          <t>Hydata</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>16°30'</t>
+          <t>49°30'</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>16°40'</t>
+          <t>5°00'</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>16.6667</t>
-        </is>
-      </c>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Altar of Eros promontory</t>
+          <t>where the Moschios river branches. Viminacium, legion</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>66°30'</t>
+          <t>46°30'</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>16°00'</t>
+          <t>4°00'</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>16.0</t>
-        </is>
-      </c>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Apokopa</t>
+          <t>the more northerly of this division flows into Pontos by the mouth called Boreios, located</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>70°00'</t>
+          <t>56°20'</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3°00'</t>
+          <t>6°50'</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>56.3333</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3.0</t>
-        </is>
-      </c>
+          <t>6.8333</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Small shore</t>
+          <t>the mor southerly of this division flows into Pontos by the mouth called Narakion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>78°00'</t>
+          <t>56°10'</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1°00' S</t>
+          <t>6°20'</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>56.1667</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+          <t>6.3333</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Great shore</t>
+          <t>Sacred mouth of the Istros river, Pteron promontory</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>76°00'</t>
+          <t>56°20'</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2°00' S</t>
+          <t>6°00'</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>56.3333</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-2.0</t>
-        </is>
-      </c>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Essina trading post</t>
+          <t>Istros city</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>73°30'</t>
+          <t>55°40'</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3°30' S</t>
+          <t>6°00'</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>55.6667</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-3.5</t>
-        </is>
-      </c>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Koloe city</t>
+          <t>Pherai</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69°00'</t>
+          <t>49°30'</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>4°15'</t>
+          <t>30°15'</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4.25</t>
-        </is>
-      </c>
+          <t>30.25</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5999,44 +7526,47 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Maste city</t>
+          <t>Mt. Ousalaiton or Ousaleton, the end points of which are at</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>65°00'</t>
+          <t>37°00'</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>4°15'</t>
+          <t>38°00'</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4.25</t>
-        </is>
-      </c>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6046,40 +7576,47 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>which the Triton river flows, and in it these lakes: Tritonitis</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>55°00'</t>
+          <t>38°40'</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>8°30'</t>
+          <t>39°40'</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>38.6667</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>8.5</t>
-        </is>
-      </c>
+          <t>39.6667</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6089,12 +7626,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6104,29 +7641,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>beside the lakes the so-called Pylaian mountains . 65°00' . equator and Maste mountain</t>
+          <t>Anthedon</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>68°00'</t>
+          <t>64°50'</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>5°00'</t>
+          <t>51°40'</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>64.8333</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5.0</t>
-        </is>
-      </c>
+          <t>51.6667</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6136,40 +7676,47 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>same meridian until the limit, at</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>68°</t>
+          <t>51°15'</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>12°20' S</t>
+          <t>3°10'</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>51.25</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-12.3333</t>
-        </is>
-      </c>
+          <t>3.1667</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6179,279 +7726,317 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Those that have come to our knowledge are as follows: Mount Dauchis, the centre of which is</t>
+          <t>which the Darados river flows, midpoint</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>15°</t>
+          <t>27°</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>8°25' S</t>
+          <t>10°</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-8.4167</t>
-        </is>
-      </c>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>mentioned point, i.e</t>
+          <t>south of the river Thupai</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61°00'</t>
+          <t>16°30'</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>31°15'</t>
+          <t>16°40'</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>16.6667</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Nigritis-See</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>4.06.14.04</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>at the city Kytoron of the Pontos</t>
+          <t>Apokopa</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61°00'</t>
+          <t>70°00'</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>33°45'</t>
+          <t>3°00'</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>33.75</t>
-        </is>
-      </c>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kadmos mountain</t>
+          <t>Great shore</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>59°40'</t>
+          <t>76°00'</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>37°40'</t>
+          <t>2°00' S</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>59.6667</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>37.6667</t>
-        </is>
-      </c>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Laodikeia katakekaumene</t>
+          <t>Koloe city</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>63°40'</t>
+          <t>69°00'</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>39°40'</t>
+          <t>4°15'</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>63.6667</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>39.6667</t>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Garbato-Gebirge (Mitte)</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>4.07.26.04</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Neapolis</t>
+          <t>Those that have come to our knowledge are as follows: Mount Dauchis, the centre of which is</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>62°40'</t>
+          <t>15°</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>48°45'</t>
+          <t>8°25' S</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>62.6667</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>48.75</t>
-        </is>
-      </c>
+          <t>-8.4167</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6461,44 +8046,47 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>along the line of the Moschikos mountains and to the terminal</t>
+          <t>mentioned point, i.e</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>73°00'</t>
+          <t>61°00'</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>44°30'</t>
+          <t>31°15'</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>44.5</t>
-        </is>
-      </c>
+          <t>31.25</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ptolemy_geographica/topostext/unmapped_review.xlsx
+++ b/ptolemy_geographica/topostext/unmapped_review.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K86"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2162,72 +2162,68 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5.06.01.13</t>
+          <t>2.06.70.04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Euphrat (Biegung nach Osten)</t>
+          <t>Baecula (Becula)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>river</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AS01</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Euphrat</t>
-        </is>
-      </c>
+          <t>EU02</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>31.3</v>
+        <v>30.6</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>north, it is then deflected from the east, the location of which is</t>
+          <t>Egosa</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>5.6.1.4</t>
+          <t>2.6.70.3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2.06.70.04</t>
+          <t>2.08.04.03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Baecula (Becula)</t>
+          <t>Cebenna-Gebirge (Mitte)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2237,18 +2233,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>EU02</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>EU03</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Cevennen</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2256,29 +2256,29 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Egosa</t>
+          <t>East of the Arverni until the northward turn of the river Rhone, is the tribe of the Aedui and their cities: Augustodunum</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2.6.70.3</t>
+          <t>2.8.12.1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2.08.04.03</t>
+          <t>2.15.04.03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cebenna-Gebirge (Mitte)</t>
+          <t>Solva</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>mountain</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2288,22 +2288,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>EU03</t>
+          <t>EU05</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cevennen</t>
+          <t>Esztergom</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2311,24 +2311,24 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>East of the Arverni until the northward turn of the river Rhone, is the tribe of the Aedui and their cities: Augustodunum</t>
+          <t>The next turn at Carpis, which is the most northerly of all</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2.8.12.1</t>
+          <t>2.11.3.9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2.15.04.03</t>
+          <t>2.15.08.02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Solva</t>
+          <t>Sallis (Saldis)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2346,19 +2346,15 @@
           <t>EU05</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Esztergom</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>44.6666666666667</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2366,24 +2362,24 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>The next turn at Carpis, which is the most northerly of all</t>
+          <t>Sidrona</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.11.3.9</t>
+          <t>2.16.10.5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2.15.08.02</t>
+          <t>2.15.08.05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sallis (Saldis)</t>
+          <t>Sirmium*</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2401,15 +2397,19 @@
           <t>EU05</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Sremska Mitrovica</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.8333333333333</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>44.6666666666667</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -2417,29 +2417,29 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Sidrona</t>
+          <t>that point where the Arabus river flows into the Danube, forming those borders to which we have referred; on the south by Illyria which extends from the indicated terminus as far as the bend in the Danube near which the Savos river empties into it</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2.16.10.5</t>
+          <t>2.15.1.1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2.15.08.05</t>
+          <t>3.01.80.02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sirmium*</t>
+          <t>Diomedische Inseln (5)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>island</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>EU05</t>
+          <t>EU06</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sremska Mitrovica</t>
+          <t>Isole di Tremiti</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>44.8333333333333</t>
+          <t>40.6666666666667</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -2472,54 +2472,50 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>that point where the Arabus river flows into the Danube, forming those borders to which we have referred; on the south by Illyria which extends from the indicated terminus as far as the bend in the Danube near which the Savos river empties into it</t>
+          <t>of the Maurrucini on the same gulf mouth of the Aternus river</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2.15.1.1</t>
+          <t>3.1.20.1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3.01.80.02</t>
+          <t>4.05.76.03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Diomedische Inseln (5)</t>
+          <t>Argaiu</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>island</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>EU06</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Isole di Tremiti</t>
-        </is>
-      </c>
+          <t>AF03</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>40.6666666666667</t>
+          <t>61.4166666666667</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>31.6666666666667</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -2527,80 +2523,84 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>of the Maurrucini on the same gulf mouth of the Aternus river</t>
+          <t>the Sebennytic mouth</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>3.1.20.1</t>
+          <t>4.5.10.3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4.05.76.03</t>
+          <t>2.08.03.02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Argaiu</t>
+          <t>Sequana (Mitte)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>river</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AF03</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>EU03</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Seine</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>61.4166666666667</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>31.6666666666667</t>
+          <t>49.3333333333333</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>30.6</v>
+        <v>30.1</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>the Sebennytic mouth</t>
+          <t>Below these are the Vessones, with their city similarly on the eastern side of the SequanaRiver, Augusta Vessonum</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>4.5.10.3</t>
+          <t>2.9.6.4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2.08.03.02</t>
+          <t>2.07.11.02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sequana (Mitte)</t>
+          <t>Divona</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>river</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2615,42 +2615,42 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Seine</t>
+          <t>Cahors</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>49.3333333333333</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Below these are the Vessones, with their city similarly on the eastern side of the SequanaRiver, Augusta Vessonum</t>
+          <t>to these the Cadurci and their city Dueona</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2.9.6.4</t>
+          <t>2.7.6.6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2.07.11.02</t>
+          <t>2.15.06.02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Divona</t>
+          <t>Servitium*</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2665,22 +2665,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>EU03</t>
+          <t>EU05</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cahors</t>
+          <t>Bosanska Gradiska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>42.3333333333333</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -2688,24 +2688,24 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>to these the Cadurci and their city Dueona</t>
+          <t>On the north, by the above-mentioned border of Noricum and by the part of the Danubebetween Cetium mountain and the junction with the Arabon river</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2.7.6.6</t>
+          <t>2.14.1.2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2.15.06.02</t>
+          <t>4.07.25.03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Servitium*</t>
+          <t>Maste</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2715,27 +2715,23 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>EU05</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Bosanska Gradiska</t>
-        </is>
-      </c>
+          <t>AF04</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>42.3333333333333</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -2743,24 +2739,24 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>On the north, by the above-mentioned border of Noricum and by the part of the Danubebetween Cetium mountain and the junction with the Arabon river</t>
+          <t>the more eastern lake</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2.14.1.2</t>
+          <t>4.7.24.2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4.07.25.03</t>
+          <t>4.03.28.05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Maste</t>
+          <t>Mileum</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2775,43 +2771,47 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AF04</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
+          <t>AF02</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mila</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>26.6666666666667</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>30.3333333333333</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>30</v>
+        <v>28.6</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>the more eastern lake</t>
+          <t>Lares</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>4.7.24.2</t>
+          <t>4.3.28.4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4.03.28.05</t>
+          <t>2.15.04.06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mileum</t>
+          <t>Vetus Salina</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2821,52 +2821,52 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AF02</t>
+          <t>EU05</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mila</t>
+          <t>Adony</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>26.6666666666667</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>30.3333333333333</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>28.6</v>
+        <v>27.7</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Lares</t>
+          <t>Sidrona</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>4.3.28.4</t>
+          <t>2.16.10.5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2.15.04.06</t>
+          <t>2.15.06.03</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Vetus Salina</t>
+          <t>Iovalia</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2886,17 +2886,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Adony</t>
+          <t>Valpovo</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.3333333333333</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -2904,29 +2904,29 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Sidrona</t>
+          <t>Salvia</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2.16.10.5</t>
+          <t>2.16.9.8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2.15.06.03</t>
+          <t>2.15.02.05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Iovalia</t>
+          <t>Danuvius (Einmündung des Dravus)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>river</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2941,42 +2941,42 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Valpovo</t>
+          <t>Donau (Einmündung der Drau)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>42.3333333333333</t>
+          <t>44.3333333333333</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.6666666666667</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>27.7</v>
+        <v>27</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Salvia</t>
+          <t>Adra</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2.16.9.8</t>
+          <t>2.16.10.1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2.15.02.05</t>
+          <t>2.15.02.14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Danuvius (Einmündung des Dravus)</t>
+          <t>Danuvius (Biegung bei Acumincum)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2996,17 +2996,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Donau (Einmündung der Drau)</t>
+          <t>Donau</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>44.3333333333333</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>45.6666666666667</t>
+          <t>45.4166666666667</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -3014,29 +3014,29 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Adra</t>
+          <t>that point where the Arabus river flows into the Danube, forming those borders to which we have referred; on the south by Illyria which extends from the indicated terminus as far as the bend in the Danube near which the Savos river empties into it</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2.16.10.1</t>
+          <t>2.15.1.1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2.15.02.14</t>
+          <t>2.15.08.01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Danuvius (Biegung bei Acumincum)</t>
+          <t>Mursa (Mursa*)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>river</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3051,17 +3051,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Donau</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>45.4166666666667</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -3069,24 +3069,24 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>that point where the Arabus river flows into the Danube, forming those borders to which we have referred; on the south by Illyria which extends from the indicated terminus as far as the bend in the Danube near which the Savos river empties into it</t>
+          <t>The bend at Curta</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2.15.1.1</t>
+          <t>2.11.3.8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2.15.08.01</t>
+          <t>2.03.21.02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mursa (Mursa*)</t>
+          <t>Salinae</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3101,47 +3101,43 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>EU05</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Osijek</t>
-        </is>
-      </c>
+          <t>EU01</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>55.6666666666667</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>27</v>
+        <v>25.7</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>The bend at Curta</t>
+          <t>Navalia</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2.11.3.8</t>
+          <t>2.11.13.2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2.03.21.02</t>
+          <t>2.15.04.05</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Salinae</t>
+          <t>Aquincum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3156,18 +3152,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>EU01</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
+          <t>EU05</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>55.6666666666667</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -3175,24 +3175,24 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Navalia</t>
+          <t>Anavum</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2.11.13.2</t>
+          <t>2.11.15.19</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2.15.04.05</t>
+          <t>2.11.29.11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Aquincum</t>
+          <t>Bergium</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3207,154 +3207,154 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>EU05</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Budapest</t>
-        </is>
-      </c>
+          <t>EU04</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>25.7</v>
+        <v>24.8</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Anavum</t>
+          <t>further the mountains called the Sudeta, whose extremities occupy the positions</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2.11.15.19</t>
+          <t>2.11.5.9</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2.11.29.11</t>
+          <t>4.03.18.05</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bergium</t>
+          <t>Uasalaiton-Gebirge (W-Ende)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>EU04</t>
+          <t>AF02</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>24.8</v>
+        <v>24.4</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>further the mountains called the Sudeta, whose extremities occupy the positions</t>
+          <t>Tisurus</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2.11.5.9</t>
+          <t>4.3.38.5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4.03.18.05</t>
+          <t>2.15.05.03</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Uasalaiton-Gebirge (W-Ende)</t>
+          <t>Cornacum</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mountain</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AF02</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
+          <t>EU05</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Sotin</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>44.3333333333333</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>24.4</v>
+        <v>24.2</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Tisurus</t>
+          <t>Nedinon</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>4.3.38.5</t>
+          <t>2.16.10.8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2.15.05.03</t>
+          <t>2.15.02.16</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cornacum</t>
+          <t>Danuvius (Biegung bei Rittium)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>river</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3369,47 +3369,47 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sotin</t>
+          <t>Donau</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>44.3333333333333</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>24.2</v>
+        <v>24</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Nedinon</t>
+          <t>that point where the Arabus river flows into the Danube, forming those borders to which we have referred; on the south by Illyria which extends from the indicated terminus as far as the bend in the Danube near which the Savos river empties into it</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2.16.10.8</t>
+          <t>2.15.1.1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2.15.02.16</t>
+          <t>2.15.07.02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Danuvius (Biegung bei Rittium)</t>
+          <t>Cibalae</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>river</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3424,72 +3424,68 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Donau</t>
+          <t>Vinkovci</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
+          <t>43.0</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
           <t>45.5</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>45.0</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>24</v>
+        <v>22.5</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>that point where the Arabus river flows into the Danube, forming those borders to which we have referred; on the south by Illyria which extends from the indicated terminus as far as the bend in the Danube near which the Savos river empties into it</t>
+          <t>Adra</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2.15.1.1</t>
+          <t>2.16.10.1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2.15.07.02</t>
+          <t>4.03.20.03</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cibalae</t>
+          <t>Thizibi-Berg</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>EU05</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Vinkovci</t>
-        </is>
-      </c>
+          <t>AF02</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -3497,80 +3493,80 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Adra</t>
+          <t>Mt. Thizibi</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2.16.10.1</t>
+          <t>4.3.20.2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4.03.20.03</t>
+          <t>2.06.76.03</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Thizibi-Berg</t>
+          <t>Inseln der Götter (2)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>mountain</t>
+          <t>island</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AF02</t>
+          <t>EU02</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>4.66666666666667</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>43.3333333333333</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>22.5</v>
+        <v>21.4</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Mt. Thizibi</t>
+          <t>Limios river mouth</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>4.3.20.2</t>
+          <t>2.6.1.4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2.06.76.03</t>
+          <t>3.05.06.02</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Inseln der Götter (2)</t>
+          <t>Sarmatische Berge (S-Ende)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>island</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3580,18 +3576,22 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>EU02</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
+          <t>EU08</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Westkarpaten</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>4.66666666666667</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>43.3333333333333</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="I60" t="n">
@@ -3599,24 +3599,24 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Limios river mouth</t>
+          <t>There are the following cities among the Migratory Iazuges: Ouskenon</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2.6.1.4</t>
+          <t>3.7.2.1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3.05.06.02</t>
+          <t>4.06.09.03</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sarmatische Berge (S-Ende)</t>
+          <t>Kapha-Gebirge (Mitte)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3626,103 +3626,103 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>EU08</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Westkarpaten</t>
-        </is>
-      </c>
+          <t>AF04</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>There are the following cities among the Migratory Iazuges: Ouskenon</t>
+          <t>which the Stacheir river flows, forming lake Klonia beside it, midpoint</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>3.7.2.1</t>
+          <t>4.6.8.3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4.06.09.03</t>
+          <t>2.15.07.01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Kapha-Gebirge (Mitte)</t>
+          <t>Mursella</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>mountain</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AF04</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
+          <t>EU05</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Petrijevci</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>20.7</v>
+        <v>19.3</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>which the Stacheir river flows, forming lake Klonia beside it, midpoint</t>
+          <t>Salvia</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>4.6.8.3</t>
+          <t>2.16.9.8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2.15.07.01</t>
+          <t>2.15.05.04</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mursella</t>
+          <t>Acumincum</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3742,42 +3742,42 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Petrijevci</t>
+          <t>Stari Slankamen</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>44.8333333333333</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.3333333333333</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>19.3</v>
+        <v>18.3</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Salvia</t>
+          <t>that point where the Arabus river flows into the Danube, forming those borders to which we have referred; on the south by Illyria which extends from the indicated terminus as far as the bend in the Danube near which the Savos river empties into it</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2.16.9.8</t>
+          <t>2.15.1.1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2.15.05.04</t>
+          <t>2.15.05.05</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Acumincum</t>
+          <t>Rittium</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3797,17 +3797,17 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stari Slankamen</t>
+          <t>Surduk</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>44.8333333333333</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>45.3333333333333</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -3827,42 +3827,38 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2.15.05.05</t>
+          <t>4.07.11.08</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Rittium</t>
+          <t>Kleiner Strand</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>coast</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>EU05</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Surduk</t>
-        </is>
-      </c>
+          <t>AF04</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -3870,75 +3866,79 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>that point where the Arabus river flows into the Danube, forming those borders to which we have referred; on the south by Illyria which extends from the indicated terminus as far as the bend in the Danube near which the Savos river empties into it</t>
+          <t>South horn promontory</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2.15.1.1</t>
+          <t>4.7.11.6</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4.07.11.08</t>
+          <t>2.15.04.07</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kleiner Strand</t>
+          <t>Lussonium</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>coast</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AF04</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
+          <t>EU05</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Dunakömlöd</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>18.3</v>
+        <v>16.9</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>South horn promontory</t>
+          <t>Sidrona</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>4.7.11.6</t>
+          <t>2.16.10.5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2.15.04.07</t>
+          <t>4.02.12.03</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Lussonium</t>
+          <t>Grenzpunkt (Africa, Inneres Libyen, Mauretania Caesariensis)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3948,47 +3948,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>EU05</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Dunakömlöd</t>
-        </is>
-      </c>
+          <t>AF01</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>27.8333333333333</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>16.9</v>
+        <v>16.4</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Sidrona</t>
+          <t>It is bounded on the east by Africa along the Ampsagas river to that point at</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2.16.10.5</t>
+          <t>4.2.12.1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4.02.12.03</t>
+          <t>4.03.01.05</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4008,7 +4004,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AF01</t>
+          <t>AF02</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -4039,68 +4035,68 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4.03.01.05</t>
+          <t>2.15.02.12</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Grenzpunkt (Africa, Inneres Libyen, Mauretania Caesariensis)</t>
+          <t>Danuvius (Biegung bei Cornacum)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>river</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AF02</t>
+          <t>EU05</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>27.8333333333333</t>
+          <t>44.4166666666667</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>16.4</v>
+        <v>15.3</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>It is bounded on the east by Africa along the Ampsagas river to that point at</t>
+          <t>Nedinon</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>4.2.12.1</t>
+          <t>2.16.10.8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2.15.02.12</t>
+          <t>2.15.05.01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Danuvius (Biegung bei Cornacum)</t>
+          <t>Lugio</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>river</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4113,40 +4109,44 @@
           <t>EU05</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Dunaszekcsö</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>44.4166666666667</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>15.3</v>
+        <v>15</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Nedinon</t>
+          <t>Sidrona</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2.16.10.8</t>
+          <t>2.16.10.5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2.15.05.01</t>
+          <t>2.15.05.02</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Lugio</t>
+          <t>Teutoburgium</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4166,47 +4166,47 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dunaszekcsö</t>
+          <t>Dalj</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>45.6666666666667</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Sidrona</t>
+          <t>Bournon</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2.16.10.5</t>
+          <t>2.16.10.4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2.15.05.02</t>
+          <t>3.05.15.04</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Teutoburgium</t>
+          <t>Amadoka-Gebirge</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4216,52 +4216,48 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>EU05</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Dalj</t>
-        </is>
-      </c>
+          <t>EU08</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>45.6666666666667</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>14.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Bournon</t>
+          <t>Bykos river mouth</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2.16.10.4</t>
+          <t>3.5.4.4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3.05.15.04</t>
+          <t>2.15.07.04</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Amadoka-Gebirge</t>
+          <t>Vacontium (Vocantium)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>mountain</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4271,48 +4267,48 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>EU08</t>
+          <t>EU05</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Bykos river mouth</t>
+          <t>The bend at Curta</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>3.5.4.4</t>
+          <t>2.11.3.8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2.15.07.04</t>
+          <t>3.05.02.01</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Vacontium (Vocantium)</t>
+          <t>Vistula-Mündung</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>river_mouth</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4322,93 +4318,93 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>EU05</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
+          <t>EU08</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Weichsel-Mündung</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>46.5</t>
-        </is>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>The bend at Curta</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>2.11.3.8</t>
-        </is>
-      </c>
+          <t>56.0</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3.05.02.01</t>
+          <t>4.06.08.05</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Vistula-Mündung</t>
+          <t>Sagapola-Gebirge (Mitte)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>river_mouth</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>EU08</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Weichsel-Mündung</t>
-        </is>
-      </c>
+          <t>AF04</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>56.0</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Thuelath or Thuoilath</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>4.6.24.2</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4.06.08.05</t>
+          <t>4.06.27.05</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sagapola-Gebirge (Mitte)</t>
+          <t>Uellegeia (Uelegeia)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>mountain</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4424,37 +4420,27 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>22.0</t>
-        </is>
-      </c>
-      <c r="I76" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>Thuelath or Thuoilath</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>4.6.24.2</t>
-        </is>
-      </c>
+          <t>11.6666666666667</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4.06.27.05</t>
+          <t>4.06.28.01</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Uellegeia (Uelegeia)</t>
+          <t>Thupai (Thuppai)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4475,32 +4461,42 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>11.6666666666667</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+          <t>16.6666666666667</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Nigeira metropolis</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>4.6.27.4</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4.06.28.01</t>
+          <t>4.07.11.06</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Thupai (Thuppai)</t>
+          <t>Apokopon (Apokopa)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>coast</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4516,12 +4512,12 @@
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>16.6666666666667</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -4529,24 +4525,24 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Nigeira metropolis</t>
+          <t>Zingis promontory</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>4.6.27.4</t>
+          <t>4.7.11.3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4.07.11.06</t>
+          <t>4.07.11.09</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Apokopon (Apokopa)</t>
+          <t>Grosser Strand</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4567,37 +4563,27 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="I79" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Zingis promontory</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>4.7.11.3</t>
-        </is>
-      </c>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4.07.11.09</t>
+          <t>4.07.11.10</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Grosser Strand</t>
+          <t>Essina (Essinadu)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4615,15 +4601,19 @@
           <t>AF04</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Wasin</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.1666666666667</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -4633,17 +4623,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4.07.11.10</t>
+          <t>4.07.24.03</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Essina (Essinadu)</t>
+          <t>Koloe-See</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>coast</t>
+          <t>lake</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4656,19 +4646,15 @@
           <t>AF04</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Wasin</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>73.1666666666667</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -4678,17 +4664,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4.07.24.03</t>
+          <t>4.07.25.02</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Koloe-See</t>
+          <t>Koloe</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>lake</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4704,32 +4690,42 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Maste city</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>4.7.25.3</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4.07.25.02</t>
+          <t>4.07.26.07</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Koloe</t>
+          <t>Pylaia-Gebirge</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4745,37 +4741,27 @@
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>4.25</t>
-        </is>
-      </c>
-      <c r="I83" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>Maste city</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>4.7.25.3</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4.07.26.07</t>
+          <t>4.07.26.08</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pylaia-Gebirge</t>
+          <t>Maste-Berg</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4796,12 +4782,12 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -4811,12 +4797,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4.07.26.08</t>
+          <t>4.08.06.01</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Maste-Berg</t>
+          <t>Dauchis-Gebirge (Mitte)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4837,58 +4823,17 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>-13.0</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>4.08.06.01</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Dauchis-Gebirge (Mitte)</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>mountain</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Africa</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AF04</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>-13.0</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4901,7 +4846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4983,60 +4928,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Legion I Athena (Minerva) and then Traiane Legion</t>
+          <t>Hierapolis</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>28°30'</t>
+          <t>71°15'</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>50°35'</t>
+          <t>30°15'</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>71.25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50.5833</t>
+          <t>30.25</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>44.2</v>
+        <v>44.4</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Bonna, Legio I Minervia</t>
+          <t>Obaira</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2.09.16.01</t>
+          <t>5.19.07.01</t>
         </is>
       </c>
     </row>
@@ -5048,55 +4993,55 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Edeta and/or Leiria</t>
+          <t>Legion I Athena (Minerva) and then Traiane Legion</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14°20'</t>
+          <t>28°30'</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>38°25'</t>
+          <t>50°35'</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>14.3333</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>38.4167</t>
+          <t>50.5833</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>43.9</v>
+        <v>44.2</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Edeta bzw. Liria</t>
+          <t>Bonna, Legio I Minervia</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2.06.63.14</t>
+          <t>2.09.16.01</t>
         </is>
       </c>
     </row>
@@ -5108,115 +5053,115 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Forum Segusianorum</t>
+          <t>Edeta and/or Leiria</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20°30'</t>
+          <t>14°20'</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>45°30'</t>
+          <t>38°25'</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>14.3333</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>38.4167</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>43.1</v>
+        <v>43.9</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Forum Segusiavorum</t>
+          <t>Edeta bzw. Liria</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2.08.14.08</t>
+          <t>2.06.63.14</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>mouths of the river Rhenus: Mouths of the river Vidrus</t>
+          <t>Arrade</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>27°20'</t>
+          <t>71°30'</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>54°45'</t>
+          <t>30°15'</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>27.3333</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>54.75</t>
+          <t>30.25</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>43</v>
+        <v>43.7</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Vidrus-Mündung</t>
+          <t>Artemita</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2.11.01.05</t>
+          <t>5.19.07.02</t>
         </is>
       </c>
     </row>
@@ -5228,162 +5173,162 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>the northernmost point</t>
+          <t>Forum Segusianorum</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>44°20'</t>
+          <t>20°30'</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>58°20'</t>
+          <t>45°30'</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>44.3333</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>58.3333</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>42.8</v>
+        <v>43.1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Scandia N</t>
+          <t>Forum Segusiavorum</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2.11.34.04</t>
+          <t>2.08.14.08</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Argidaua</t>
+          <t>mouths of the river Rhenus: Mouths of the river Vidrus</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>46°30'</t>
+          <t>27°20'</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>45°15'</t>
+          <t>54°45'</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>27.3333</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>54.75</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>42.8</v>
+        <v>43</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Lizisis (Aizisis)</t>
+          <t>Vidrus-Mündung</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>3.08.09.02</t>
+          <t>2.11.01.05</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Emporikos kolpos</t>
+          <t>the northernmost point</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>6°30'</t>
+          <t>44°20'</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>34°20'</t>
+          <t>58°20'</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>44.3333</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>34.3333</t>
+          <t>58.3333</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -5391,59 +5336,59 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Handelsbucht</t>
+          <t>Scandia N</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>4.01.02.05</t>
+          <t>2.11.34.04</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kadmos mountain</t>
+          <t>Argidaua</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>59°40'</t>
+          <t>46°30'</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>37°40'</t>
+          <t>45°15'</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>59.6667</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>37.6667</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -5451,132 +5396,132 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Grenzpunkt (eigentliches Asien, Lykien 2)</t>
+          <t>Lizisis (Aizisis)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>5.02.12.04</t>
+          <t>3.08.09.02</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>along the line of the Moschikos mountains and to the terminal</t>
+          <t>Emporikos kolpos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>73°00'</t>
+          <t>6°30'</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>44°30'</t>
+          <t>34°20'</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>34.3333</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>42.1</v>
+        <v>42.8</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Xyline</t>
+          <t>Handelsbucht</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>5.06.06.08</t>
+          <t>4.01.02.05</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>to these the Cadurci and their city Dueona</t>
+          <t>Kadmos mountain</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>19°00'</t>
+          <t>59°40'</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>46°15'</t>
+          <t>37°40'</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>59.6667</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>37.6667</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>41.6</v>
+        <v>42.8</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Cossium</t>
+          <t>Grenzpunkt (eigentliches Asien, Lykien 2)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2.07.15.02</t>
+          <t>5.02.12.04</t>
         </is>
       </c>
     </row>
@@ -5588,55 +5533,55 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Laodikeia katakekaumene</t>
+          <t>along the line of the Moschikos mountains and to the terminal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>63°40'</t>
+          <t>73°00'</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>39°40'</t>
+          <t>44°30'</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>63.6667</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>39.6667</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>40.8</v>
+        <v>42.1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>verbranntes' Laodikeia</t>
+          <t>Xyline</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>5.04.10.11</t>
+          <t>5.06.06.08</t>
         </is>
       </c>
     </row>
@@ -5648,115 +5593,115 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>are the Catuvellauni, among whom are the towns: Salinae</t>
+          <t>to these the Cadurci and their city Dueona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>20°45'</t>
+          <t>19°00'</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>55°50'</t>
+          <t>46°15'</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>55.8333</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>39.7</v>
+        <v>41.6</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Metaris-Ästuar</t>
+          <t>Cossium</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2.03.06.07</t>
+          <t>2.07.15.02</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>The eastern side adjoins the part of Lugdunensis by the Liger River until its head</t>
+          <t>Laodikeia katakekaumene</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20°00'</t>
+          <t>63°40'</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>44°30'</t>
+          <t>39°40'</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>63.6667</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>39.6667</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>39.7</v>
+        <v>40.8</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Tolosa</t>
+          <t>verbranntes' Laodikeia</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2.10.09.05</t>
+          <t>5.04.10.11</t>
         </is>
       </c>
     </row>
@@ -5768,42 +5713,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>The southern side is bounded by the part on this side of Narbonensis as far as the mentioned end point by Aquitania, the Cemmena mountains, mid-point</t>
+          <t>are the Catuvellauni, among whom are the towns: Salinae</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>20°20'</t>
+          <t>20°45'</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>44°30'</t>
+          <t>55°50'</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>20.3333</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>55.8333</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -5811,12 +5756,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Tolosa</t>
+          <t>Metaris-Ästuar</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2.10.09.05</t>
+          <t>2.03.06.07</t>
         </is>
       </c>
     </row>
@@ -5828,171 +5773,175 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saitabis</t>
+          <t>The eastern side adjoins the part of Lugdunensis by the Liger River until its head</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>13°10'</t>
+          <t>20°00'</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>37°00'</t>
+          <t>44°30'</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>13.1667</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>39.4</v>
+        <v>39.7</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Saetabis-Mündung</t>
+          <t>Tolosa</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2.06.14.07</t>
+          <t>2.10.09.05</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>The southern side is bounded by the part on this side of Narbonensis as far as the mentioned end point by Aquitania, the Cemmena mountains, mid-point</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>21°00'</t>
+          <t>20°20'</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>26°00'</t>
+          <t>44°30'</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.3333</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>36.7</v>
+        <v>39.7</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Phruraison-Gebirge (O-Ende)</t>
+          <t>Tolosa</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>4.02.16.02</t>
+          <t>2.10.09.05</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>a different starting point, the towns are Thudaca</t>
+          <t>Saitabis</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>19°10'</t>
+          <t>13°10'</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>32°20'</t>
+          <t>37°00'</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>19.1667</t>
+          <t>13.1667</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>32.3333</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>36.7</v>
+        <v>39.4</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Tigis</t>
+          <t>Saetabis-Mündung</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>4.02.30.02</t>
+          <t>2.06.14.07</t>
         </is>
       </c>
     </row>
@@ -6004,12 +5953,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -6020,22 +5969,22 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>55°00'</t>
+          <t>21°00'</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>8°30'</t>
+          <t>26°00'</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -6043,12 +5992,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Äthiopische Berge (S-Ende)</t>
+          <t>Phruraison-Gebirge (O-Ende)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>4.07.26.03</t>
+          <t>4.02.16.02</t>
         </is>
       </c>
     </row>
@@ -6060,175 +6009,167 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Altar of Eros promontory</t>
+          <t>a different starting point, the towns are Thudaca</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>66°30'</t>
+          <t>19°10'</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>16°00'</t>
+          <t>32°20'</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>19.1667</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>32.3333</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>34.9</v>
+        <v>36.7</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Ptolemais Theron*</t>
+          <t>Tigis</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>4.07.07.01</t>
+          <t>4.02.30.02</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Bergium</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>33°00'</t>
+          <t>55°00'</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>49°20'</t>
+          <t>8°30'</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>49.3333</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>33.4</v>
+        <v>36.7</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Alpes (N-Spitzen)</t>
+          <t>Äthiopische Berge (S-Ende)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2.11.07.05</t>
+          <t>4.07.26.03</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>The Nitriotai, and the Oasita dwell in the parts still further to the south, at</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>59°30'</t>
+          <t>80°00'</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>29°30'</t>
+          <t>30°40'</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.6667</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>32.7</v>
+        <v>36.7</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Pharos</t>
+          <t>Teredon*</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>4.05.76.02</t>
+          <t>5.20.05.04</t>
         </is>
       </c>
     </row>
@@ -6240,115 +6181,115 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bunthum</t>
+          <t>Altar of Eros promontory</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>36°15'</t>
+          <t>66°30'</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>27°20'</t>
+          <t>16°00'</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>36.25</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>27.3333</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>32.1</v>
+        <v>34.9</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Bunthon</t>
+          <t>Ptolemais Theron*</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>4.03.36.07</t>
+          <t>4.07.07.01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>beside the lakes the so-called Pylaian mountains . 65°00' . equator and Maste mountain</t>
+          <t>Bergium</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>68°00'</t>
+          <t>33°00'</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>5°00'</t>
+          <t>49°20'</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>49.3333</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>26</v>
+        <v>33.4</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Garbato-Gebirge (Mitte)</t>
+          <t>Alpes (N-Spitzen)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>4.07.26.04</t>
+          <t>2.11.07.05</t>
         </is>
       </c>
     </row>
@@ -6360,115 +6301,115 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aigimoros island</t>
+          <t>The Nitriotai, and the Oasita dwell in the parts still further to the south, at</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>34°15'</t>
+          <t>59°30'</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>33°30'</t>
+          <t>29°30'</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>24.4</v>
+        <v>32.7</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Kap Hermaia</t>
+          <t>Pharos</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>4.03.08.01</t>
+          <t>4.05.76.02</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Neapolis</t>
+          <t>Bunthum</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>62°40'</t>
+          <t>36°15'</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>48°45'</t>
+          <t>27°20'</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>62.6667</t>
+          <t>36.25</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>27.3333</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>20</v>
+        <v>32.1</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Phanagoria</t>
+          <t>Bunthon</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>5.09.06.02</t>
+          <t>4.03.36.07</t>
         </is>
       </c>
     </row>
@@ -6485,127 +6426,127 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Essina trading post</t>
+          <t>beside the lakes the so-called Pylaian mountains . 65°00' . equator and Maste mountain</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>73°30'</t>
+          <t>68°00'</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>3°30' S</t>
+          <t>5°00'</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>18.3</v>
+        <v>26</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Sarapion</t>
+          <t>Garbato-Gebirge (Mitte)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>4.07.11.11</t>
+          <t>4.07.26.04</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Of the Pelagonians: Audaristos</t>
+          <t>mountain of Pieria flows north and then turns east at this position</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>48°40'</t>
+          <t>71°37'</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>50°05'</t>
+          <t>30°00'</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>48.6667</t>
+          <t>71.6167</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>50.0833</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>18</v>
+        <v>25.7</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Porolisson</t>
+          <t>Artemita</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>3.08.06.04</t>
+          <t>5.19.07.02</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6615,100 +6556,100 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>turn</t>
+          <t>Aigimoros island</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>39°10'</t>
+          <t>34°15'</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>59°10'</t>
+          <t>33°30'</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>39.1667</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>59.1667</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>15.3</v>
+        <v>24.4</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Erste Landspitze nach der Landspitze</t>
+          <t>Kap Hermaia</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2.11.03.04</t>
+          <t>4.03.08.01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pontia island</t>
+          <t>Neapolis</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>45°20'</t>
+          <t>62°40'</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20°15'</t>
+          <t>48°45'</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>45.3333</t>
+          <t>62.6667</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>15.3</v>
+        <v>20</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Kinyps (O-Quelle)</t>
+          <t>Phanagoria</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>4.06.11.03</t>
+          <t>5.09.06.02</t>
         </is>
       </c>
     </row>
@@ -6720,175 +6661,175 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>which the Subos river flows, midpoint</t>
+          <t>Essina trading post</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>20°20'</t>
+          <t>73°30'</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>22°</t>
+          <t>3°30' S</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>20.3333</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>15.3</v>
+        <v>18.3</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Byntha</t>
+          <t>Sarapion</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>4.06.25.05</t>
+          <t>4.07.11.11</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Small shore</t>
+          <t>Of the Pelagonians: Audaristos</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>78°00'</t>
+          <t>48°40'</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1°00' S</t>
+          <t>50°05'</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>48.6667</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>50.0833</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Horn des Südens</t>
+          <t>Porolisson</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>4.07.11.07</t>
+          <t>3.08.06.04</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>at the city Kytoron of the Pontos</t>
+          <t>turn</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61°00'</t>
+          <t>39°10'</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>33°45'</t>
+          <t>59°10'</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>39.1667</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>59.1667</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>13.8</v>
+        <v>15.3</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Xanthos-Mündung</t>
+          <t>Erste Landspitze nach der Landspitze</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>5.03.02.07</t>
+          <t>2.11.03.04</t>
         </is>
       </c>
     </row>
@@ -6900,12 +6841,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -6913,38 +6854,42 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Pontia island</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>68°</t>
+          <t>45°20'</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>12°20' S</t>
+          <t>20°15'</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>45.3333</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-12.3333</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>12.2</v>
+        <v>15.3</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Mondgebirge (O-Ende)</t>
+          <t>Kinyps (O-Quelle)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>4.08.03.06</t>
+          <t>4.06.11.03</t>
         </is>
       </c>
     </row>
@@ -6961,50 +6906,50 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Uellegeia</t>
+          <t>which the Subos river flows, midpoint</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>28°30'</t>
+          <t>20°20'</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>16°40'</t>
+          <t>22°</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>20.3333</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>16.6667</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>12</v>
+        <v>15.3</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Tagama</t>
+          <t>Byntha</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>4.06.27.06</t>
+          <t>4.06.25.05</t>
         </is>
       </c>
     </row>
@@ -7021,297 +6966,333 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Maste city</t>
+          <t>Small shore</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>65°00'</t>
+          <t>78°00'</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4°15'</t>
+          <t>1°00' S</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Koloe</t>
+          <t>Horn des Südens</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>4.07.25.02</t>
+          <t>4.07.11.07</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mosa River the Menapii and their city Castellum</t>
+          <t>at the city Kytoron of the Pontos</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25°00'</t>
+          <t>61°00'</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>22°15'</t>
+          <t>33°45'</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>22.25</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
+          <t>33.75</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Xanthos-Mündung</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>5.03.02.07</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Piroum</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>51°15'</t>
+          <t>68°</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>6°00'</t>
+          <t>12°20' S</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>51.25</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
+          <t>-12.3333</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Mondgebirge (O-Ende)</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>4.08.03.06</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hydata</t>
+          <t>Uellegeia</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>49°30'</t>
+          <t>28°30'</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>5°00'</t>
+          <t>16°40'</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+          <t>16.6667</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>12</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Tagama</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>4.06.27.06</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>where the Moschios river branches. Viminacium, legion</t>
+          <t>Maste city</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>46°30'</t>
+          <t>65°00'</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>4°00'</t>
+          <t>4°15'</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>8</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Koloe</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>4.07.25.02</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>the more northerly of this division flows into Pontos by the mouth called Boreios, located</t>
+          <t>Mosa River the Menapii and their city Castellum</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>56°20'</t>
+          <t>25°00'</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>6°50'</t>
+          <t>22°15'</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>56.3333</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>6.8333</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -7326,42 +7307,42 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>the mor southerly of this division flows into Pontos by the mouth called Narakion</t>
+          <t>Piroum</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>56°10'</t>
+          <t>51°15'</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>6°20'</t>
+          <t>6°00'</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>56.1667</t>
+          <t>51.25</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>6.3333</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
@@ -7376,42 +7357,42 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sacred mouth of the Istros river, Pteron promontory</t>
+          <t>Hydata</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>56°20'</t>
+          <t>49°30'</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>6°00'</t>
+          <t>5°00'</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>56.3333</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
@@ -7426,7 +7407,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -7441,27 +7422,27 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Istros city</t>
+          <t>where the Moschios river branches. Viminacium, legion</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>55°40'</t>
+          <t>46°30'</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>6°00'</t>
+          <t>4°00'</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>55.6667</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
@@ -7476,42 +7457,42 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pherai</t>
+          <t>the more northerly of this division flows into Pontos by the mouth called Boreios, located</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>49°30'</t>
+          <t>56°20'</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>30°15'</t>
+          <t>6°50'</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>56.3333</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>6.8333</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -7521,47 +7502,47 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mt. Ousalaiton or Ousaleton, the end points of which are at</t>
+          <t>the mor southerly of this division flows into Pontos by the mouth called Narakion</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>37°00'</t>
+          <t>56°10'</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>38°00'</t>
+          <t>6°20'</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>56.1667</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>6.3333</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -7571,47 +7552,47 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>which the Triton river flows, and in it these lakes: Tritonitis</t>
+          <t>Sacred mouth of the Istros river, Pteron promontory</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>38°40'</t>
+          <t>56°20'</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>39°40'</t>
+          <t>6°00'</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>38.6667</t>
+          <t>56.3333</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>39.6667</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -7621,47 +7602,47 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Anthedon</t>
+          <t>Istros city</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>64°50'</t>
+          <t>55°40'</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>51°40'</t>
+          <t>6°00'</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>64.8333</t>
+          <t>55.6667</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>51.6667</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -7671,47 +7652,47 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>same meridian until the limit, at</t>
+          <t>Pherai</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>51°15'</t>
+          <t>49°30'</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>3°10'</t>
+          <t>30°15'</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>51.25</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3.1667</t>
+          <t>30.25</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -7726,42 +7707,42 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>which the Darados river flows, midpoint</t>
+          <t>Mt. Ousalaiton or Ousaleton, the end points of which are at</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>27°</t>
+          <t>37°00'</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>10°</t>
+          <t>38°00'</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -7776,12 +7757,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7791,42 +7772,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>south of the river Thupai</t>
+          <t>which the Triton river flows, and in it these lakes: Tritonitis</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>16°30'</t>
+          <t>38°40'</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>16°40'</t>
+          <t>39°40'</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>38.6667</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>16.6667</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Nigritis-See</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>4.06.14.04</t>
-        </is>
-      </c>
+          <t>39.6667</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7836,12 +7807,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7851,27 +7822,27 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Apokopa</t>
+          <t>Anthedon</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>70°00'</t>
+          <t>64°50'</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>3°00'</t>
+          <t>51°40'</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>64.8333</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>51.6667</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
@@ -7886,42 +7857,42 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Great shore</t>
+          <t>same meridian until the limit, at</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>76°00'</t>
+          <t>51°15'</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2°00' S</t>
+          <t>3°10'</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>51.25</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>3.1667</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -7936,12 +7907,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7951,42 +7922,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Koloe city</t>
+          <t>which the Darados river flows, midpoint</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69°00'</t>
+          <t>27°</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>4°15'</t>
+          <t>10°</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>4.25</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Garbato-Gebirge (Mitte)</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>4.07.26.04</t>
-        </is>
-      </c>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7996,12 +7957,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8011,82 +7972,352 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Those that have come to our knowledge are as follows: Mount Dauchis, the centre of which is</t>
+          <t>south of the river Thupai</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>15°</t>
+          <t>16°30'</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>8°25' S</t>
+          <t>16°40'</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-8.4167</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
+          <t>16.6667</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Nigritis-See</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>4.06.14.04</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>mentioned point, i.e</t>
+          <t>Apokopa</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61°00'</t>
+          <t>70°00'</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>31°15'</t>
+          <t>3°00'</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Great shore</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>76°00'</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2°00' S</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Koloe city</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>69°00'</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>4°15'</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Garbato-Gebirge (Mitte)</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>4.07.26.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Those that have come to our knowledge are as follows: Mount Dauchis, the centre of which is</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>15°</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>8°25' S</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>-8.4167</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>mentioned point, i.e</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>61°00'</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>31°15'</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>61.0</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>31.25</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>mouth of the Chorseas river: Kaisareia Stratonos</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>60°15'</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>32°30'</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>60.25</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>32.5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ptolemy_geographica/topostext/unmapped_review.xlsx
+++ b/ptolemy_geographica/topostext/unmapped_review.xlsx
@@ -8710,7 +8710,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>coast</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">

--- a/ptolemy_geographica/topostext/unmapped_review.xlsx
+++ b/ptolemy_geographica/topostext/unmapped_review.xlsx
@@ -1222,7 +1222,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>coast</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>coast</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>coast</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>coast</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>river</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>coast</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>coast</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>river</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>coast</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>coast</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -9394,107 +9394,107 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>the northernmost point</t>
+          <t>Altar of Eros promontory</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>44°20'</t>
+          <t>66°30'</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>58°20'</t>
+          <t>16°00'</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>44.3333</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>58.3333</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Scandia N</t>
+          <t>Ptolemais Theron*</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2.11.34.04</t>
+          <t>4.07.07.01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Argidaua</t>
+          <t>the northernmost point</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>46°30'</t>
+          <t>44°20'</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>45°15'</t>
+          <t>58°20'</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>44.3333</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>58.3333</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -9502,59 +9502,59 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Lizisis (Aizisis)</t>
+          <t>Scandia N</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3.08.09.02</t>
+          <t>2.11.34.04</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Emporikos kolpos</t>
+          <t>Argidaua</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>6°30'</t>
+          <t>46°30'</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>34°20'</t>
+          <t>45°15'</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>34.3333</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -9562,59 +9562,59 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Handelsbucht</t>
+          <t>Lizisis (Aizisis)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4.01.02.05</t>
+          <t>3.08.09.02</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kadmos mountain</t>
+          <t>Emporikos kolpos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>59°40'</t>
+          <t>6°30'</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>37°40'</t>
+          <t>34°20'</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>59.6667</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>37.6667</t>
+          <t>34.3333</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -9622,59 +9622,59 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Grenzpunkt (eigentliches Asien, Lykien 2)</t>
+          <t>Handelsbucht</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>5.02.12.04</t>
+          <t>4.01.02.05</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hierakon kome</t>
+          <t>Kadmos mountain</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>84°30'</t>
+          <t>59°40'</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20°30'</t>
+          <t>37°40'</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>59.6667</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>37.6667</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -9682,59 +9682,59 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Dorf der Adler</t>
+          <t>Grenzpunkt (eigentliches Asien, Lykien 2)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>6.07.36.01</t>
+          <t>5.02.12.04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Great Coast (Aigialos Megas)</t>
+          <t>Hierakon kome</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>130°00'</t>
+          <t>84°30'</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4°20'</t>
+          <t>20°30'</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.3333</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -9742,12 +9742,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Helios-Hafen</t>
+          <t>Dorf der Adler</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>7.04.06.02</t>
+          <t>6.07.36.01</t>
         </is>
       </c>
     </row>
@@ -9759,12 +9759,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9774,387 +9774,387 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Boukephala</t>
+          <t>Great Coast (Aigialos Megas)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>125°30'</t>
+          <t>130°00'</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>30°20'</t>
+          <t>4°20'</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>30.3333</t>
+          <t>4.3333</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>42.6</v>
+        <v>42.8</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Bukephala*</t>
+          <t>Helios-Hafen</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>7.01.46.05</t>
+          <t>7.04.06.02</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>along the line of the Moschikos mountains and to the terminal</t>
+          <t>Boukephala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>73°00'</t>
+          <t>125°30'</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>44°30'</t>
+          <t>30°20'</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>30.3333</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>42.1</v>
+        <v>42.6</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Xyline</t>
+          <t>Bukephala*</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>5.06.06.08</t>
+          <t>7.01.46.05</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Soxestra or Sokstra</t>
+          <t>along the line of the Moschikos mountains and to the terminal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>118°30'</t>
+          <t>73°00'</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>25°45'</t>
+          <t>44°30'</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Soxstra</t>
+          <t>Xyline</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>6.21.05.06</t>
+          <t>5.06.06.08</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>to these the Cadurci and their city Dueona</t>
+          <t>Soxestra or Sokstra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>19°00'</t>
+          <t>118°30'</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>46°15'</t>
+          <t>25°45'</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>118.5</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>41.6</v>
+        <v>42</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Cossium</t>
+          <t>Soxstra</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2.07.15.02</t>
+          <t>6.21.05.06</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tharrha</t>
+          <t>to these the Cadurci and their city Dueona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>162°00'</t>
+          <t>19°00'</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1°20' S</t>
+          <t>46°15'</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.3333</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Tharra</t>
+          <t>Cossium</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>7.02.25.04</t>
+          <t>2.07.15.02</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Laodikeia katakekaumene</t>
+          <t>Tharrha</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>63°40'</t>
+          <t>162°00'</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>39°40'</t>
+          <t>1°20' S</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>63.6667</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>39.6667</t>
+          <t>-1.3333</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>40.8</v>
+        <v>41.5</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>verbranntes' Laodikeia</t>
+          <t>Tharra</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>5.04.10.11</t>
+          <t>7.02.25.04</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>of the Aboukaians: Hieros gulf</t>
+          <t>Laodikeia katakekaumene</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>78°15'</t>
+          <t>63°40'</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>28°15'</t>
+          <t>39°40'</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>78.25</t>
+          <t>63.6667</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>39.6667</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Heiliger Golf</t>
+          <t>verbranntes' Laodikeia</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>6.07.19.02</t>
+          <t>5.04.10.11</t>
         </is>
       </c>
     </row>
@@ -10179,42 +10179,42 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>the part at the lake formed by it which is called Arachotos Krene (fountain)— lies in</t>
+          <t>of the Aboukaians: Hieros gulf</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>115°00'</t>
+          <t>78°15'</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>28°40'</t>
+          <t>28°15'</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>115.0</t>
+          <t>78.25</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>28.6667</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -10222,59 +10222,59 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Arachotos-Brunnen</t>
+          <t>Heiliger Golf</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>6.20.02.04</t>
+          <t>6.07.19.02</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Confluence of the Zaradros and Bibasis</t>
+          <t>the part at the lake formed by it which is called Arachotos Krene (fountain)— lies in</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>131°00'</t>
+          <t>115°00'</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>34°00'</t>
+          <t>28°40'</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>28.6667</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -10282,72 +10282,72 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Bibasis-Quellen</t>
+          <t>Arachotos-Brunnen</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>7.01.26.09</t>
+          <t>6.20.02.04</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>are the Catuvellauni, among whom are the towns: Salinae</t>
+          <t>Confluence of the Zaradros and Bibasis</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>20°45'</t>
+          <t>131°00'</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>55°50'</t>
+          <t>34°00'</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>55.8333</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>39.7</v>
+        <v>40.8</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Metaris-Ästuar</t>
+          <t>Bibasis-Quellen</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2.03.06.07</t>
+          <t>7.01.26.09</t>
         </is>
       </c>
     </row>
@@ -10359,42 +10359,42 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>The eastern side adjoins the part of Lugdunensis by the Liger River until its head</t>
+          <t>are the Catuvellauni, among whom are the towns: Salinae</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>20°00'</t>
+          <t>20°45'</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>44°30'</t>
+          <t>55°50'</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>55.8333</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -10402,12 +10402,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Tolosa</t>
+          <t>Metaris-Ästuar</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2.10.09.05</t>
+          <t>2.03.06.07</t>
         </is>
       </c>
     </row>
@@ -10419,12 +10419,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>The southern side is bounded by the part on this side of Narbonensis as far as the mentioned end point by Aquitania, the Cemmena mountains, mid-point</t>
+          <t>The eastern side adjoins the part of Lugdunensis by the Liger River until its head</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>20°20'</t>
+          <t>20°00'</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>20.3333</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -10474,47 +10474,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sozoa</t>
+          <t>The southern side is bounded by the part on this side of Narbonensis as far as the mentioned end point by Aquitania, the Cemmena mountains, mid-point</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>80°50'</t>
+          <t>20°20'</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>41°10'</t>
+          <t>44°30'</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>80.8333</t>
+          <t>20.3333</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>41.1667</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -10522,132 +10522,132 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Azaga (Azata)</t>
+          <t>Tolosa</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>6.02.09.02</t>
+          <t>2.10.09.05</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saitabis</t>
+          <t>Sozoa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>13°10'</t>
+          <t>80°50'</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>37°00'</t>
+          <t>41°10'</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>13.1667</t>
+          <t>80.8333</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>41.1667</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>39.4</v>
+        <v>39.7</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Saetabis-Mündung</t>
+          <t>Azaga (Azata)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2.06.14.07</t>
+          <t>6.02.09.02</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Charax Pasinou</t>
+          <t>Saitabis</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>80°00'</t>
+          <t>13°10'</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>31°00'</t>
+          <t>37°00'</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>13.1667</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>38.6</v>
+        <v>39.4</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Charax des Pasines</t>
+          <t>Saetabis-Mündung</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>6.03.02.04</t>
+          <t>2.06.14.07</t>
         </is>
       </c>
     </row>
@@ -10659,12 +10659,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -10674,27 +10674,27 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Arikaka</t>
+          <t>Charax Pasinou</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>113°00'</t>
+          <t>80°00'</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>31°20'</t>
+          <t>31°00'</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>31.3333</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -10702,12 +10702,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Arikada</t>
+          <t>Charax des Pasines</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>6.19.04.05</t>
+          <t>6.03.02.04</t>
         </is>
       </c>
     </row>
@@ -10719,55 +10719,55 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saoue palace</t>
+          <t>Arikaka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>76°00'</t>
+          <t>113°00'</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>12°00'</t>
+          <t>31°20'</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>31.3333</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>38.3</v>
+        <v>38.6</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Sabe* (Saue*)</t>
+          <t>Arikada</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>6.07.42.01</t>
+          <t>6.19.04.05</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10779,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -10794,27 +10794,27 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Asta</t>
+          <t>Saoue palace</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>117°30'</t>
+          <t>76°00'</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>30°40'</t>
+          <t>12°00'</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>117.5</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>30.6667</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -10822,189 +10822,193 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Arachotos*</t>
+          <t>Sabe* (Saue*)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>6.20.05.01</t>
+          <t>6.07.42.01</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Asta</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>117°30'</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>30°40'</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>117.5</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30.6667</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Arachotos*</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>6.20.05.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>The sources of the other river are in</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>142°00'</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>27°00'</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>142.0</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>27.0</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="J34" t="n">
         <v>38.1</v>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>Namenloser Fluss zum Ganges (Einmündung  vom 
 Uxenton-Gebirge her)</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>7.01.30.05</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Branch of the Indus towards Arachosia</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>121°30'</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>27°30'</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>121.5</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>27.5</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Namenloser Fluss zum Indus, Einmündung von Arachosien her</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>7.01.28.05</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Branch of the Indus towards Arachosia</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>21°00'</t>
+          <t>121°30'</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>26°00'</t>
+          <t>27°30'</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>27.5</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>36.7</v>
+        <v>37.1</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Phruraison-Gebirge (O-Ende)</t>
+          <t>Namenloser Fluss zum Indus, Einmündung von Arachosien her</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>4.02.16.02</t>
+          <t>7.01.28.05</t>
         </is>
       </c>
     </row>
@@ -11021,37 +11025,33 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>a different starting point, the towns are Thudaca</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>19°10'</t>
+          <t>21°00'</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>32°20'</t>
+          <t>26°00'</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>19.1667</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>32.3333</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Tigis</t>
+          <t>Phruraison-Gebirge (O-Ende)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>4.02.30.02</t>
+          <t>4.02.16.02</t>
         </is>
       </c>
     </row>
@@ -11076,38 +11076,42 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>a different starting point, the towns are Thudaca</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>55°00'</t>
+          <t>19°10'</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>8°30'</t>
+          <t>32°20'</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>19.1667</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>32.3333</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -11115,55 +11119,55 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Äthiopische Berge (S-Ende)</t>
+          <t>Tigis</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>4.07.26.03</t>
+          <t>4.02.30.02</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>80°00'</t>
+          <t>55°00'</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>30°40'</t>
+          <t>8°30'</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>30.6667</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -11171,72 +11175,68 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Teredon*</t>
+          <t>Äthiopische Berge (S-Ende)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>5.20.05.04</t>
+          <t>4.07.26.03</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Altar of Eros promontory</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>66°30'</t>
+          <t>80°00'</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>16°00'</t>
+          <t>30°40'</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>30.6667</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>34.9</v>
+        <v>36.7</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Ptolemais Theron*</t>
+          <t>Teredon*</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>4.07.07.01</t>
+          <t>5.20.05.04</t>
         </is>
       </c>
     </row>
@@ -12023,137 +12023,137 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Chabouata</t>
+          <t>S. Cape Maleou Kolon</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>89°15'</t>
+          <t>163°00'</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>22°00'</t>
+          <t>2°</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>89.25</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>28.1</v>
+        <v>29.4</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Rhabana (Rhathana)</t>
+          <t>Perimula</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>6.07.33.05</t>
+          <t>7.02.05.10</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>its point of junction with the Ganges in</t>
+          <t>Chabouata</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>144°00'</t>
+          <t>89°15'</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>26°00'</t>
+          <t>22°00'</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>89.25</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>27.5</v>
+        <v>28.1</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Namenloser Fluss (südl.) zum Ganges (Einmündung vom Bepyrron-Gebirge)</t>
+          <t>Rhabana (Rhathana)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>7.02.09.05</t>
+          <t>6.07.33.05</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -12163,263 +12163,267 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>western limit point of the island</t>
+          <t>its point of junction with the Ganges in</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>85°00'</t>
+          <t>144°00'</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>10°30'</t>
+          <t>26°00'</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>27</v>
+        <v>27.5</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Eristhe (Etisthe)</t>
+          <t>Namenloser Fluss (südl.) zum Ganges (Einmündung vom Bepyrron-Gebirge)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>6.07.10.05</t>
+          <t>7.02.09.05</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>beside the lakes the so-called Pylaian mountains . 65°00' . equator and Maste mountain</t>
+          <t>western limit point of the island</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>68°00'</t>
+          <t>85°00'</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>5°00'</t>
+          <t>10°30'</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Garbato-Gebirge (Mitte)</t>
+          <t>Eristhe (Etisthe)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>4.07.26.04</t>
+          <t>6.07.10.05</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>mountain of Pieria flows north and then turns east at this position</t>
+          <t>beside the lakes the so-called Pylaian mountains . 65°00' . equator and Maste mountain</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>71°37'</t>
+          <t>68°00'</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>30°00'</t>
+          <t>5°00'</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>71.6167</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>25.7</v>
+        <v>26</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Artemita</t>
+          <t>Garbato-Gebirge (Mitte)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>5.19.07.02</t>
+          <t>4.07.26.04</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aigimoros island</t>
+          <t>mountain of Pieria flows north and then turns east at this position</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>34°15'</t>
+          <t>71°37'</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>33°30'</t>
+          <t>30°00'</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>71.6167</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>24.4</v>
+        <v>25.7</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Kap Hermaia</t>
+          <t>Artemita</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>4.03.08.01</t>
+          <t>5.19.07.02</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Aigimoros island</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>101°00'</t>
+          <t>34°15'</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>33°00'</t>
+          <t>33°30'</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -12427,12 +12431,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Masdoranon-Gebirge (S-Ende)</t>
+          <t>Kap Hermaia</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>6.05.01.06</t>
+          <t>4.03.08.01</t>
         </is>
       </c>
     </row>
@@ -12444,12 +12448,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12457,29 +12461,25 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Nagara metropolis</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>84°45'</t>
+          <t>101°00'</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>18°30'</t>
+          <t>33°00'</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>84.75</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -12487,72 +12487,72 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Iula</t>
+          <t>Masdoranon-Gebirge (S-Ende)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>6.07.37.04</t>
+          <t>6.05.01.06</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kanagora</t>
+          <t>Nagara metropolis</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>135°00'</t>
+          <t>84°45'</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>30°40'</t>
+          <t>18°30'</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>84.75</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>30.6667</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>24</v>
+        <v>24.4</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Sannaba</t>
+          <t>Iula</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>7.01.52.03</t>
+          <t>6.07.37.04</t>
         </is>
       </c>
     </row>
@@ -12564,55 +12564,55 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>S. Cape Maleou Kolon</t>
+          <t>Kanagora</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>163°00'</t>
+          <t>135°00'</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2°</t>
+          <t>30°40'</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>30.6667</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>21.4</v>
+        <v>24</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Perimula</t>
+          <t>Sannaba</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>7.02.05.10</t>
+          <t>7.01.52.03</t>
         </is>
       </c>
     </row>
@@ -14275,12 +14275,12 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Anubingara</t>
+          <t>Poduke (Peduke)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>7.04.04.01</t>
+          <t>7.04.10.04</t>
         </is>
       </c>
     </row>

--- a/ptolemy_geographica/topostext/unmapped_review.xlsx
+++ b/ptolemy_geographica/topostext/unmapped_review.xlsx
@@ -3837,7 +3837,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>island</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
